--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Garretts Reports\Sales Report App\Excell Sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svr01\home\gfetzer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB0AAA1-4129-47F6-B4B0-EA7473431854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A625FFA3-DD0F-4E4B-9393-00C4AF933D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1887" uniqueCount="339">
   <si>
     <t>BGC10</t>
   </si>
@@ -1439,7 +1439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6055176-08B8-4018-B9DF-7F26AB5DB49D}">
-  <dimension ref="A1:K688"/>
+  <dimension ref="A1:K689"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -9191,13 +9191,13 @@
         <v>276</v>
       </c>
       <c r="B572" s="3" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="C572" s="6">
-        <v>41.99</v>
+        <v>106.14</v>
       </c>
       <c r="D572" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.25">
@@ -9205,13 +9205,13 @@
         <v>276</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="C573" s="6">
-        <v>82</v>
+        <v>41.99</v>
       </c>
       <c r="D573" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.25">
@@ -9219,10 +9219,10 @@
         <v>276</v>
       </c>
       <c r="B574" s="3" t="s">
-        <v>256</v>
+        <v>58</v>
       </c>
       <c r="C574" s="6">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="D574" t="s">
         <v>145</v>
@@ -9233,13 +9233,13 @@
         <v>276</v>
       </c>
       <c r="B575" s="3" t="s">
-        <v>112</v>
+        <v>256</v>
       </c>
       <c r="C575" s="6">
-        <v>28.05</v>
+        <v>28</v>
       </c>
       <c r="D575" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.25">
@@ -9247,7 +9247,7 @@
         <v>276</v>
       </c>
       <c r="B576" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C576" s="6">
         <v>28.05</v>
@@ -9261,7 +9261,7 @@
         <v>276</v>
       </c>
       <c r="B577" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C577" s="6">
         <v>28.05</v>
@@ -9275,27 +9275,27 @@
         <v>276</v>
       </c>
       <c r="B578" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C578" s="6">
-        <v>11.2</v>
+        <v>28.05</v>
       </c>
       <c r="D578" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A581" t="s">
-        <v>144</v>
-      </c>
-      <c r="B581" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C581" s="6">
-        <v>29.87</v>
-      </c>
-      <c r="D581" t="s">
-        <v>136</v>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A579" t="s">
+        <v>276</v>
+      </c>
+      <c r="B579" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C579" s="6">
+        <v>11.2</v>
+      </c>
+      <c r="D579" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.25">
@@ -9303,13 +9303,13 @@
         <v>144</v>
       </c>
       <c r="B582" s="3" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C582" s="6">
-        <v>199</v>
+        <v>29.87</v>
       </c>
       <c r="D582" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.25">
@@ -9317,13 +9317,13 @@
         <v>144</v>
       </c>
       <c r="B583" s="3" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C583" s="6">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="D583" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.25">
@@ -9331,10 +9331,10 @@
         <v>144</v>
       </c>
       <c r="B584" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C584" s="6">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="D584" t="s">
         <v>142</v>
@@ -9345,10 +9345,10 @@
         <v>144</v>
       </c>
       <c r="B585" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C585" s="6">
-        <v>309</v>
+        <v>189</v>
       </c>
       <c r="D585" t="s">
         <v>142</v>
@@ -9359,13 +9359,13 @@
         <v>144</v>
       </c>
       <c r="B586" s="3" t="s">
-        <v>212</v>
+        <v>31</v>
       </c>
       <c r="C586" s="6">
-        <v>175</v>
+        <v>309</v>
       </c>
       <c r="D586" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.25">
@@ -9373,10 +9373,10 @@
         <v>144</v>
       </c>
       <c r="B587" s="3" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C587" s="6">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="D587" t="s">
         <v>144</v>
@@ -9387,13 +9387,13 @@
         <v>144</v>
       </c>
       <c r="B588" s="3" t="s">
-        <v>57</v>
+        <v>202</v>
       </c>
       <c r="C588" s="6">
-        <v>59.99</v>
+        <v>134</v>
       </c>
       <c r="D588" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.25">
@@ -9401,10 +9401,10 @@
         <v>144</v>
       </c>
       <c r="B589" s="3" t="s">
-        <v>256</v>
+        <v>57</v>
       </c>
       <c r="C589" s="6">
-        <v>32.99</v>
+        <v>59.99</v>
       </c>
       <c r="D589" t="s">
         <v>145</v>
@@ -9415,10 +9415,10 @@
         <v>144</v>
       </c>
       <c r="B590" s="3" t="s">
-        <v>58</v>
+        <v>256</v>
       </c>
       <c r="C590" s="6">
-        <v>129</v>
+        <v>32.99</v>
       </c>
       <c r="D590" t="s">
         <v>145</v>
@@ -9429,10 +9429,10 @@
         <v>144</v>
       </c>
       <c r="B591" s="3" t="s">
-        <v>257</v>
+        <v>58</v>
       </c>
       <c r="C591" s="6">
-        <v>149.99</v>
+        <v>129</v>
       </c>
       <c r="D591" t="s">
         <v>145</v>
@@ -9443,13 +9443,13 @@
         <v>144</v>
       </c>
       <c r="B592" s="3" t="s">
-        <v>59</v>
+        <v>257</v>
       </c>
       <c r="C592" s="6">
-        <v>47.99</v>
+        <v>149.99</v>
       </c>
       <c r="D592" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.25">
@@ -9457,10 +9457,10 @@
         <v>144</v>
       </c>
       <c r="B593" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C593" s="6">
-        <v>39.99</v>
+        <v>47.99</v>
       </c>
       <c r="D593" t="s">
         <v>146</v>
@@ -9471,13 +9471,13 @@
         <v>144</v>
       </c>
       <c r="B594" s="3" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="C594" s="6">
         <v>39.99</v>
       </c>
       <c r="D594" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.25">
@@ -9485,7 +9485,10 @@
         <v>144</v>
       </c>
       <c r="B595" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
+      </c>
+      <c r="C595" s="6">
+        <v>39.99</v>
       </c>
       <c r="D595" t="s">
         <v>151</v>
@@ -9496,27 +9499,24 @@
         <v>144</v>
       </c>
       <c r="B596" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D596" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A597" t="s">
+        <v>144</v>
+      </c>
+      <c r="B597" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="C596" s="6">
+      <c r="C597" s="6">
         <v>36.950000000000003</v>
       </c>
-      <c r="D596" t="s">
+      <c r="D597" t="s">
         <v>173</v>
-      </c>
-    </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A599" t="s">
-        <v>288</v>
-      </c>
-      <c r="B599" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C599" s="6">
-        <v>18</v>
-      </c>
-      <c r="D599" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.25">
@@ -9524,10 +9524,10 @@
         <v>288</v>
       </c>
       <c r="B600" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C600" s="6">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="D600" t="s">
         <v>139</v>
@@ -9538,10 +9538,10 @@
         <v>288</v>
       </c>
       <c r="B601" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C601" s="6">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D601" t="s">
         <v>139</v>
@@ -9552,10 +9552,10 @@
         <v>288</v>
       </c>
       <c r="B602" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C602" s="6">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="D602" t="s">
         <v>139</v>
@@ -9566,10 +9566,10 @@
         <v>288</v>
       </c>
       <c r="B603" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C603" s="6">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="D603" t="s">
         <v>139</v>
@@ -9580,10 +9580,10 @@
         <v>288</v>
       </c>
       <c r="B604" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C604" s="6">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="D604" t="s">
         <v>139</v>
@@ -9594,10 +9594,10 @@
         <v>288</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C605" s="6">
-        <v>239</v>
+        <v>155</v>
       </c>
       <c r="D605" t="s">
         <v>139</v>
@@ -9608,10 +9608,10 @@
         <v>288</v>
       </c>
       <c r="B606" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C606" s="6">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="D606" t="s">
         <v>139</v>
@@ -9622,10 +9622,10 @@
         <v>288</v>
       </c>
       <c r="B607" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C607" s="6">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="D607" t="s">
         <v>139</v>
@@ -9636,10 +9636,10 @@
         <v>288</v>
       </c>
       <c r="B608" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C608" s="6">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="D608" t="s">
         <v>139</v>
@@ -9650,10 +9650,10 @@
         <v>288</v>
       </c>
       <c r="B609" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C609" s="6">
-        <v>285</v>
+        <v>210</v>
       </c>
       <c r="D609" t="s">
         <v>139</v>
@@ -9664,10 +9664,10 @@
         <v>288</v>
       </c>
       <c r="B610" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C610" s="6">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="D610" t="s">
         <v>139</v>
@@ -9678,13 +9678,13 @@
         <v>288</v>
       </c>
       <c r="B611" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C611" s="6">
-        <v>19.989999999999998</v>
+        <v>250</v>
       </c>
       <c r="D611" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.25">
@@ -9692,10 +9692,10 @@
         <v>288</v>
       </c>
       <c r="B612" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C612" s="6">
-        <v>29.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D612" t="s">
         <v>140</v>
@@ -9706,13 +9706,13 @@
         <v>288</v>
       </c>
       <c r="B613" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C613" s="6">
-        <v>155</v>
+        <v>29.99</v>
       </c>
       <c r="D613" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.25">
@@ -9720,10 +9720,10 @@
         <v>288</v>
       </c>
       <c r="B614" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C614" s="6">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="D614" t="s">
         <v>142</v>
@@ -9734,10 +9734,10 @@
         <v>288</v>
       </c>
       <c r="B615" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C615" s="6">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="D615" t="s">
         <v>142</v>
@@ -9748,10 +9748,10 @@
         <v>288</v>
       </c>
       <c r="B616" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C616" s="6">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D616" t="s">
         <v>142</v>
@@ -9762,10 +9762,10 @@
         <v>288</v>
       </c>
       <c r="B617" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C617" s="6">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="D617" t="s">
         <v>142</v>
@@ -9776,10 +9776,10 @@
         <v>288</v>
       </c>
       <c r="B618" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C618" s="6">
-        <v>260</v>
+        <v>199</v>
       </c>
       <c r="D618" t="s">
         <v>142</v>
@@ -9790,10 +9790,10 @@
         <v>288</v>
       </c>
       <c r="B619" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C619" s="6">
-        <v>389</v>
+        <v>260</v>
       </c>
       <c r="D619" t="s">
         <v>142</v>
@@ -9804,10 +9804,10 @@
         <v>288</v>
       </c>
       <c r="B620" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C620" s="6">
-        <v>399.99</v>
+        <v>389</v>
       </c>
       <c r="D620" t="s">
         <v>142</v>
@@ -9818,10 +9818,10 @@
         <v>288</v>
       </c>
       <c r="B621" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C621" s="6">
-        <v>89.23</v>
+        <v>399.99</v>
       </c>
       <c r="D621" t="s">
         <v>142</v>
@@ -9831,28 +9831,28 @@
       <c r="A622" t="s">
         <v>288</v>
       </c>
-      <c r="B622" s="3">
-        <v>6102</v>
+      <c r="B622" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="C622" s="6">
-        <v>44</v>
+        <v>89.23</v>
       </c>
       <c r="D622" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>288</v>
       </c>
-      <c r="B623" s="3" t="s">
-        <v>281</v>
+      <c r="B623" s="3">
+        <v>6102</v>
       </c>
       <c r="C623" s="6">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="D623" t="s">
-        <v>269</v>
+        <v>144</v>
       </c>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.25">
@@ -9860,10 +9860,10 @@
         <v>288</v>
       </c>
       <c r="B624" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C624" s="6">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D624" t="s">
         <v>269</v>
@@ -9874,10 +9874,10 @@
         <v>288</v>
       </c>
       <c r="B625" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C625" s="6">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D625" t="s">
         <v>269</v>
@@ -9888,10 +9888,10 @@
         <v>288</v>
       </c>
       <c r="B626" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C626" s="6">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D626" t="s">
         <v>269</v>
@@ -9902,10 +9902,10 @@
         <v>288</v>
       </c>
       <c r="B627" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C627" s="6">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D627" t="s">
         <v>269</v>
@@ -9916,10 +9916,10 @@
         <v>288</v>
       </c>
       <c r="B628" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C628" s="6">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="D628" t="s">
         <v>269</v>
@@ -9930,13 +9930,13 @@
         <v>288</v>
       </c>
       <c r="B629" s="3" t="s">
-        <v>55</v>
+        <v>286</v>
       </c>
       <c r="C629" s="6">
-        <v>27.99</v>
+        <v>114</v>
       </c>
       <c r="D629" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.25">
@@ -9944,10 +9944,10 @@
         <v>288</v>
       </c>
       <c r="B630" s="3" t="s">
-        <v>255</v>
+        <v>55</v>
       </c>
       <c r="C630" s="6">
-        <v>28.99</v>
+        <v>27.99</v>
       </c>
       <c r="D630" t="s">
         <v>145</v>
@@ -9958,10 +9958,10 @@
         <v>288</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>56</v>
+        <v>255</v>
       </c>
       <c r="C631" s="6">
-        <v>39.99</v>
+        <v>28.99</v>
       </c>
       <c r="D631" t="s">
         <v>145</v>
@@ -9972,10 +9972,10 @@
         <v>288</v>
       </c>
       <c r="B632" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C632" s="6">
-        <v>58</v>
+        <v>39.99</v>
       </c>
       <c r="D632" t="s">
         <v>145</v>
@@ -9986,10 +9986,10 @@
         <v>288</v>
       </c>
       <c r="B633" s="3" t="s">
-        <v>256</v>
+        <v>57</v>
       </c>
       <c r="C633" s="6">
-        <v>42.99</v>
+        <v>58</v>
       </c>
       <c r="D633" t="s">
         <v>145</v>
@@ -10000,10 +10000,10 @@
         <v>288</v>
       </c>
       <c r="B634" s="3" t="s">
-        <v>58</v>
+        <v>256</v>
       </c>
       <c r="C634" s="6">
-        <v>129</v>
+        <v>42.99</v>
       </c>
       <c r="D634" t="s">
         <v>145</v>
@@ -10014,10 +10014,10 @@
         <v>288</v>
       </c>
       <c r="B635" s="3" t="s">
-        <v>257</v>
+        <v>58</v>
       </c>
       <c r="C635" s="6">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="D635" t="s">
         <v>145</v>
@@ -10028,13 +10028,13 @@
         <v>288</v>
       </c>
       <c r="B636" s="3" t="s">
-        <v>59</v>
+        <v>257</v>
       </c>
       <c r="C636" s="6">
-        <v>54.5</v>
+        <v>180</v>
       </c>
       <c r="D636" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.25">
@@ -10042,10 +10042,10 @@
         <v>288</v>
       </c>
       <c r="B637" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C637" s="6">
-        <v>48.99</v>
+        <v>54.5</v>
       </c>
       <c r="D637" t="s">
         <v>146</v>
@@ -10056,10 +10056,10 @@
         <v>288</v>
       </c>
       <c r="B638" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C638" s="6">
-        <v>39.99</v>
+        <v>48.99</v>
       </c>
       <c r="D638" t="s">
         <v>146</v>
@@ -10070,10 +10070,10 @@
         <v>288</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C639" s="6">
-        <v>64.989999999999995</v>
+        <v>39.99</v>
       </c>
       <c r="D639" t="s">
         <v>146</v>
@@ -10084,10 +10084,10 @@
         <v>288</v>
       </c>
       <c r="B640" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C640" s="6">
-        <v>29.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="D640" t="s">
         <v>146</v>
@@ -10098,10 +10098,10 @@
         <v>288</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C641" s="6">
-        <v>28.99</v>
+        <v>29.99</v>
       </c>
       <c r="D641" t="s">
         <v>146</v>
@@ -10112,7 +10112,10 @@
         <v>288</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>176</v>
+        <v>66</v>
+      </c>
+      <c r="C642" s="6">
+        <v>28.99</v>
       </c>
       <c r="D642" t="s">
         <v>146</v>
@@ -10123,10 +10126,7 @@
         <v>288</v>
       </c>
       <c r="B643" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C643" s="6">
-        <v>29.99</v>
+        <v>176</v>
       </c>
       <c r="D643" t="s">
         <v>146</v>
@@ -10137,10 +10137,10 @@
         <v>288</v>
       </c>
       <c r="B644" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C644" s="6">
-        <v>25.99</v>
+        <v>29.99</v>
       </c>
       <c r="D644" t="s">
         <v>146</v>
@@ -10150,28 +10150,28 @@
       <c r="A645" t="s">
         <v>288</v>
       </c>
-      <c r="B645" s="3">
-        <v>6642</v>
+      <c r="B645" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="C645" s="6">
-        <v>50</v>
+        <v>25.99</v>
       </c>
       <c r="D645" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>288</v>
       </c>
-      <c r="B646" s="3" t="s">
-        <v>109</v>
+      <c r="B646" s="3">
+        <v>6642</v>
       </c>
       <c r="C646" s="6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D646" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.25">
@@ -10179,7 +10179,7 @@
         <v>288</v>
       </c>
       <c r="B647" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C647" s="6">
         <v>40</v>
@@ -10193,13 +10193,13 @@
         <v>288</v>
       </c>
       <c r="B648" s="3" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="C648" s="6">
-        <v>39.99</v>
+        <v>40</v>
       </c>
       <c r="D648" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.25">
@@ -10207,27 +10207,27 @@
         <v>288</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>287</v>
+        <v>127</v>
       </c>
       <c r="C649" s="6">
-        <v>90</v>
+        <v>39.99</v>
       </c>
       <c r="D649" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A652" t="s">
-        <v>290</v>
-      </c>
-      <c r="B652" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C652" s="6">
-        <v>42.75</v>
-      </c>
-      <c r="D652" t="s">
-        <v>139</v>
+    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A650" t="s">
+        <v>288</v>
+      </c>
+      <c r="B650" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C650" s="6">
+        <v>90</v>
+      </c>
+      <c r="D650" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.25">
@@ -10235,10 +10235,10 @@
         <v>290</v>
       </c>
       <c r="B653" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C653" s="6">
-        <v>68</v>
+        <v>42.75</v>
       </c>
       <c r="D653" t="s">
         <v>139</v>
@@ -10249,27 +10249,27 @@
         <v>290</v>
       </c>
       <c r="B654" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C654" s="6">
-        <v>82.2</v>
+        <v>68</v>
       </c>
       <c r="D654" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A656" t="s">
-        <v>304</v>
-      </c>
-      <c r="B656" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C656" s="6">
-        <v>10</v>
-      </c>
-      <c r="D656" t="s">
-        <v>140</v>
+    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A655" t="s">
+        <v>290</v>
+      </c>
+      <c r="B655" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C655" s="6">
+        <v>82.2</v>
+      </c>
+      <c r="D655" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.25">
@@ -10277,7 +10277,10 @@
         <v>304</v>
       </c>
       <c r="B657" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="C657" s="6">
+        <v>10</v>
       </c>
       <c r="D657" t="s">
         <v>140</v>
@@ -10287,14 +10290,11 @@
       <c r="A658" t="s">
         <v>304</v>
       </c>
-      <c r="B658" s="3">
-        <v>4642</v>
-      </c>
-      <c r="C658" s="6">
-        <v>18.96</v>
+      <c r="B658" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D658" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.25">
@@ -10302,10 +10302,10 @@
         <v>304</v>
       </c>
       <c r="B659" s="3">
-        <v>6642</v>
+        <v>4642</v>
       </c>
       <c r="C659" s="6">
-        <v>22.37</v>
+        <v>18.96</v>
       </c>
       <c r="D659" t="s">
         <v>148</v>
@@ -10315,14 +10315,14 @@
       <c r="A660" t="s">
         <v>304</v>
       </c>
-      <c r="B660" s="3" t="s">
-        <v>116</v>
+      <c r="B660" s="3">
+        <v>6642</v>
       </c>
       <c r="C660" s="6">
-        <v>9.1</v>
+        <v>22.37</v>
       </c>
       <c r="D660" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.25">
@@ -10330,7 +10330,7 @@
         <v>304</v>
       </c>
       <c r="B661" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C661" s="6">
         <v>9.1</v>
@@ -10339,18 +10339,18 @@
         <v>152</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A666" t="s">
-        <v>292</v>
-      </c>
-      <c r="B666" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C666" s="6">
-        <v>5</v>
-      </c>
-      <c r="D666" t="s">
-        <v>140</v>
+    <row r="662" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A662" t="s">
+        <v>304</v>
+      </c>
+      <c r="B662" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C662" s="6">
+        <v>9.1</v>
+      </c>
+      <c r="D662" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.25">
@@ -10358,7 +10358,7 @@
         <v>292</v>
       </c>
       <c r="B667" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C667" s="6">
         <v>5</v>
@@ -10367,18 +10367,18 @@
         <v>140</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A671" t="s">
-        <v>293</v>
-      </c>
-      <c r="B671" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C671" s="6">
-        <v>3.15</v>
-      </c>
-      <c r="D671" t="s">
-        <v>303</v>
+    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A668" t="s">
+        <v>292</v>
+      </c>
+      <c r="B668" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C668" s="6">
+        <v>5</v>
+      </c>
+      <c r="D668" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.25">
@@ -10386,10 +10386,10 @@
         <v>293</v>
       </c>
       <c r="B672" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C672" s="6">
-        <v>7.65</v>
+        <v>3.15</v>
       </c>
       <c r="D672" t="s">
         <v>303</v>
@@ -10400,10 +10400,10 @@
         <v>293</v>
       </c>
       <c r="B673" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C673" s="6">
-        <v>8.1</v>
+        <v>7.65</v>
       </c>
       <c r="D673" t="s">
         <v>303</v>
@@ -10414,10 +10414,10 @@
         <v>293</v>
       </c>
       <c r="B674" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C674" s="6">
-        <v>10.8</v>
+        <v>8.1</v>
       </c>
       <c r="D674" t="s">
         <v>303</v>
@@ -10428,10 +10428,10 @@
         <v>293</v>
       </c>
       <c r="B675" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C675" s="6">
-        <v>12.2</v>
+        <v>10.8</v>
       </c>
       <c r="D675" t="s">
         <v>303</v>
@@ -10442,10 +10442,10 @@
         <v>293</v>
       </c>
       <c r="B676" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C676" s="6">
-        <v>11.25</v>
+        <v>12.2</v>
       </c>
       <c r="D676" t="s">
         <v>303</v>
@@ -10456,7 +10456,7 @@
         <v>293</v>
       </c>
       <c r="B677" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C677" s="6">
         <v>11.25</v>
@@ -10470,7 +10470,7 @@
         <v>293</v>
       </c>
       <c r="B678" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C678" s="6">
         <v>11.25</v>
@@ -10479,17 +10479,17 @@
         <v>303</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A681" t="s">
-        <v>294</v>
-      </c>
-      <c r="B681" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C681" s="6">
-        <v>3.36</v>
-      </c>
-      <c r="D681" t="s">
+    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A679" t="s">
+        <v>293</v>
+      </c>
+      <c r="B679" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C679" s="6">
+        <v>11.25</v>
+      </c>
+      <c r="D679" t="s">
         <v>303</v>
       </c>
     </row>
@@ -10498,10 +10498,10 @@
         <v>294</v>
       </c>
       <c r="B682" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C682" s="6">
-        <v>10.19</v>
+        <v>3.36</v>
       </c>
       <c r="D682" t="s">
         <v>303</v>
@@ -10512,10 +10512,10 @@
         <v>294</v>
       </c>
       <c r="B683" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C683" s="6">
-        <v>14.4</v>
+        <v>10.19</v>
       </c>
       <c r="D683" t="s">
         <v>303</v>
@@ -10526,10 +10526,10 @@
         <v>294</v>
       </c>
       <c r="B684" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C684" s="6">
-        <v>14.39</v>
+        <v>14.4</v>
       </c>
       <c r="D684" t="s">
         <v>303</v>
@@ -10540,10 +10540,10 @@
         <v>294</v>
       </c>
       <c r="B685" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C685" s="6">
-        <v>11.52</v>
+        <v>14.39</v>
       </c>
       <c r="D685" t="s">
         <v>303</v>
@@ -10554,10 +10554,10 @@
         <v>294</v>
       </c>
       <c r="B686" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C686" s="6">
-        <v>12</v>
+        <v>11.52</v>
       </c>
       <c r="D686" t="s">
         <v>303</v>
@@ -10568,7 +10568,7 @@
         <v>294</v>
       </c>
       <c r="B687" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C687" s="6">
         <v>12</v>
@@ -10582,12 +10582,26 @@
         <v>294</v>
       </c>
       <c r="B688" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C688" s="6">
         <v>12</v>
       </c>
       <c r="D688" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="689" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A689" t="s">
+        <v>294</v>
+      </c>
+      <c r="B689" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C689" s="6">
+        <v>12</v>
+      </c>
+      <c r="D689" t="s">
         <v>303</v>
       </c>
     </row>

--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svr01\home\gfetzer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A625FFA3-DD0F-4E4B-9393-00C4AF933D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26BA943B-35F7-4298-BF85-653018E1F7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
   </bookViews>
@@ -903,9 +903,6 @@
     <t>Ovala-42</t>
   </si>
   <si>
-    <t>ACE Hardware</t>
-  </si>
-  <si>
     <t>Lotus Light</t>
   </si>
   <si>
@@ -1042,6 +1039,9 @@
   </si>
   <si>
     <t>RS10</t>
+  </si>
+  <si>
+    <t>ACE</t>
   </si>
 </sst>
 </file>
@@ -3056,7 +3056,7 @@
         <v>156</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C108" s="6">
         <v>5.5</v>
@@ -3486,7 +3486,7 @@
         <v>156</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C136" s="6">
         <v>16</v>
@@ -3501,7 +3501,7 @@
         <v>156</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C137" s="6">
         <v>33</v>
@@ -3756,13 +3756,13 @@
         <v>156</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C154" s="6">
         <v>22.85</v>
       </c>
       <c r="D154" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K154" s="3"/>
     </row>
@@ -3771,13 +3771,13 @@
         <v>156</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C155" s="6">
         <v>15.75</v>
       </c>
       <c r="D155" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K155" s="3"/>
     </row>
@@ -3786,13 +3786,13 @@
         <v>156</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C156" s="6">
         <v>10.5</v>
       </c>
       <c r="D156" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K156" s="3"/>
     </row>
@@ -3801,13 +3801,13 @@
         <v>156</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C157" s="6">
         <v>45</v>
       </c>
       <c r="D157" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K157" s="3"/>
     </row>
@@ -3816,13 +3816,13 @@
         <v>156</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C158" s="6">
         <v>77.5</v>
       </c>
       <c r="D158" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K158" s="3"/>
     </row>
@@ -3831,13 +3831,13 @@
         <v>156</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C159" s="6">
         <v>152.30000000000001</v>
       </c>
       <c r="D159" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K159" s="3"/>
     </row>
@@ -3846,13 +3846,13 @@
         <v>156</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C160" s="6">
         <v>273</v>
       </c>
       <c r="D160" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K160" s="3"/>
     </row>
@@ -4046,13 +4046,13 @@
         <v>156</v>
       </c>
       <c r="B174" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C174" s="6">
         <v>9.25</v>
       </c>
       <c r="D174" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -4060,13 +4060,13 @@
         <v>156</v>
       </c>
       <c r="B175" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C175" s="6">
         <v>11.4</v>
       </c>
       <c r="D175" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -4074,13 +4074,13 @@
         <v>156</v>
       </c>
       <c r="B176" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C176" s="6">
         <v>11.4</v>
       </c>
       <c r="D176" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -5346,13 +5346,13 @@
         <v>157</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C268" s="6">
         <v>92</v>
       </c>
       <c r="D268" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
@@ -5360,13 +5360,13 @@
         <v>157</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C269" s="6">
         <v>22.75</v>
       </c>
       <c r="D269" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
@@ -5374,13 +5374,13 @@
         <v>157</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C270" s="6">
         <v>18.25</v>
       </c>
       <c r="D270" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
@@ -5388,13 +5388,13 @@
         <v>157</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C271" s="6">
         <v>115</v>
       </c>
       <c r="D271" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
@@ -5402,13 +5402,13 @@
         <v>157</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C272" s="6">
         <v>227</v>
       </c>
       <c r="D272" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
@@ -6088,7 +6088,7 @@
         <v>175</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D325" t="s">
         <v>144</v>
@@ -6099,7 +6099,7 @@
         <v>175</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C326" s="6">
         <v>15.58</v>
@@ -6979,13 +6979,13 @@
         <v>181</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C393" s="6">
         <v>14.5</v>
       </c>
       <c r="D393" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
@@ -7368,7 +7368,7 @@
         <v>181</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C421" s="6">
         <v>15.99</v>
@@ -7382,7 +7382,7 @@
         <v>181</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C422" s="6">
         <v>29.99</v>
@@ -7396,7 +7396,7 @@
         <v>181</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C423" s="6">
         <v>16.989999999999998</v>
@@ -7410,7 +7410,7 @@
         <v>181</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C424" s="6">
         <v>29.99</v>
@@ -8112,7 +8112,7 @@
         <v>181</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C475" s="6">
         <v>110</v>
@@ -8126,7 +8126,7 @@
         <v>181</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C476" s="6">
         <v>98.45</v>
@@ -8140,7 +8140,7 @@
         <v>181</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C477" s="6">
         <v>139</v>
@@ -8154,7 +8154,7 @@
         <v>181</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C478" s="6">
         <v>199</v>
@@ -8168,7 +8168,7 @@
         <v>181</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C479" s="6">
         <v>169.99</v>
@@ -8182,7 +8182,7 @@
         <v>181</v>
       </c>
       <c r="B480" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C480" s="6">
         <v>239.08</v>
@@ -8196,7 +8196,7 @@
         <v>181</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C481" s="6">
         <v>219</v>
@@ -8210,7 +8210,7 @@
         <v>181</v>
       </c>
       <c r="B482" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C482" s="6">
         <v>189.99</v>
@@ -8224,7 +8224,7 @@
         <v>181</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C483" s="6">
         <v>248</v>
@@ -8238,7 +8238,7 @@
         <v>181</v>
       </c>
       <c r="B484" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C484" s="6">
         <v>297</v>
@@ -8252,7 +8252,7 @@
         <v>181</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C485" s="6">
         <v>322</v>
@@ -9107,13 +9107,13 @@
         <v>232</v>
       </c>
       <c r="B563" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C563" s="6">
         <v>5.75</v>
       </c>
       <c r="D563" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.25">
@@ -9121,13 +9121,13 @@
         <v>232</v>
       </c>
       <c r="B564" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C564" s="6">
         <v>20</v>
       </c>
       <c r="D564" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.25">
@@ -9135,13 +9135,13 @@
         <v>232</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C565" s="6">
         <v>12.5</v>
       </c>
       <c r="D565" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.25">
@@ -9149,13 +9149,13 @@
         <v>232</v>
       </c>
       <c r="B566" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C566" s="6">
         <v>77.5</v>
       </c>
       <c r="D566" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.25">
@@ -9163,13 +9163,13 @@
         <v>232</v>
       </c>
       <c r="B567" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C567" s="6">
         <v>195</v>
       </c>
       <c r="D567" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.25">
@@ -10274,7 +10274,7 @@
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B657" s="3" t="s">
         <v>22</v>
@@ -10288,7 +10288,7 @@
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B658" s="3" t="s">
         <v>23</v>
@@ -10299,7 +10299,7 @@
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B659" s="3">
         <v>4642</v>
@@ -10313,7 +10313,7 @@
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B660" s="3">
         <v>6642</v>
@@ -10327,7 +10327,7 @@
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B661" s="3" t="s">
         <v>116</v>
@@ -10341,7 +10341,7 @@
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B662" s="3" t="s">
         <v>117</v>
@@ -10355,7 +10355,7 @@
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>292</v>
+        <v>338</v>
       </c>
       <c r="B667" s="3" t="s">
         <v>22</v>
@@ -10369,7 +10369,7 @@
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>292</v>
+        <v>338</v>
       </c>
       <c r="B668" s="3" t="s">
         <v>23</v>
@@ -10383,226 +10383,226 @@
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B672" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C672" s="6">
         <v>3.15</v>
       </c>
       <c r="D672" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B673" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C673" s="6">
         <v>7.65</v>
       </c>
       <c r="D673" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B674" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C674" s="6">
         <v>8.1</v>
       </c>
       <c r="D674" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B675" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C675" s="6">
         <v>10.8</v>
       </c>
       <c r="D675" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B676" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C676" s="6">
         <v>12.2</v>
       </c>
       <c r="D676" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B677" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C677" s="6">
         <v>11.25</v>
       </c>
       <c r="D677" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B678" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C678" s="6">
         <v>11.25</v>
       </c>
       <c r="D678" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B679" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C679" s="6">
         <v>11.25</v>
       </c>
       <c r="D679" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="682" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
+        <v>293</v>
+      </c>
+      <c r="B682" s="3" t="s">
         <v>294</v>
-      </c>
-      <c r="B682" s="3" t="s">
-        <v>295</v>
       </c>
       <c r="C682" s="6">
         <v>3.36</v>
       </c>
       <c r="D682" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B683" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C683" s="6">
         <v>10.19</v>
       </c>
       <c r="D683" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="684" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B684" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C684" s="6">
         <v>14.4</v>
       </c>
       <c r="D684" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="685" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B685" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C685" s="6">
         <v>14.39</v>
       </c>
       <c r="D685" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="686" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B686" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C686" s="6">
         <v>11.52</v>
       </c>
       <c r="D686" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B687" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C687" s="6">
         <v>12</v>
       </c>
       <c r="D687" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B688" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C688" s="6">
         <v>12</v>
       </c>
       <c r="D688" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B689" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C689" s="6">
         <v>12</v>
       </c>
       <c r="D689" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>

--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svr01\home\gfetzer\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Garretts Reports\Sales Report App\Excell Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26BA943B-35F7-4298-BF85-653018E1F7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E33625B-0341-46EF-A6E9-CF33ACABBEA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1887" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="339">
   <si>
     <t>BGC10</t>
   </si>
@@ -903,6 +903,9 @@
     <t>Ovala-42</t>
   </si>
   <si>
+    <t>ACE Hardware</t>
+  </si>
+  <si>
     <t>Lotus Light</t>
   </si>
   <si>
@@ -1039,9 +1042,6 @@
   </si>
   <si>
     <t>RS10</t>
-  </si>
-  <si>
-    <t>ACE</t>
   </si>
 </sst>
 </file>
@@ -1439,7 +1439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6055176-08B8-4018-B9DF-7F26AB5DB49D}">
-  <dimension ref="A1:K689"/>
+  <dimension ref="A1:K690"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -3056,7 +3056,7 @@
         <v>156</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C108" s="6">
         <v>5.5</v>
@@ -3486,7 +3486,7 @@
         <v>156</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C136" s="6">
         <v>16</v>
@@ -3501,7 +3501,7 @@
         <v>156</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C137" s="6">
         <v>33</v>
@@ -3756,13 +3756,13 @@
         <v>156</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C154" s="6">
         <v>22.85</v>
       </c>
       <c r="D154" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K154" s="3"/>
     </row>
@@ -3771,13 +3771,13 @@
         <v>156</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C155" s="6">
         <v>15.75</v>
       </c>
       <c r="D155" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K155" s="3"/>
     </row>
@@ -3786,13 +3786,13 @@
         <v>156</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C156" s="6">
         <v>10.5</v>
       </c>
       <c r="D156" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K156" s="3"/>
     </row>
@@ -3801,13 +3801,13 @@
         <v>156</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C157" s="6">
         <v>45</v>
       </c>
       <c r="D157" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K157" s="3"/>
     </row>
@@ -3816,13 +3816,13 @@
         <v>156</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C158" s="6">
         <v>77.5</v>
       </c>
       <c r="D158" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K158" s="3"/>
     </row>
@@ -3831,13 +3831,13 @@
         <v>156</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C159" s="6">
         <v>152.30000000000001</v>
       </c>
       <c r="D159" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K159" s="3"/>
     </row>
@@ -3846,13 +3846,13 @@
         <v>156</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C160" s="6">
         <v>273</v>
       </c>
       <c r="D160" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K160" s="3"/>
     </row>
@@ -4046,13 +4046,13 @@
         <v>156</v>
       </c>
       <c r="B174" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C174" s="6">
         <v>9.25</v>
       </c>
       <c r="D174" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -4060,13 +4060,13 @@
         <v>156</v>
       </c>
       <c r="B175" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C175" s="6">
         <v>11.4</v>
       </c>
       <c r="D175" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -4074,13 +4074,13 @@
         <v>156</v>
       </c>
       <c r="B176" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C176" s="6">
         <v>11.4</v>
       </c>
       <c r="D176" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -5346,13 +5346,13 @@
         <v>157</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C268" s="6">
         <v>92</v>
       </c>
       <c r="D268" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
@@ -5360,13 +5360,13 @@
         <v>157</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C269" s="6">
         <v>22.75</v>
       </c>
       <c r="D269" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
@@ -5374,13 +5374,13 @@
         <v>157</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C270" s="6">
         <v>18.25</v>
       </c>
       <c r="D270" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
@@ -5388,13 +5388,13 @@
         <v>157</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C271" s="6">
         <v>115</v>
       </c>
       <c r="D271" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
@@ -5402,13 +5402,13 @@
         <v>157</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C272" s="6">
         <v>227</v>
       </c>
       <c r="D272" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
@@ -6088,7 +6088,7 @@
         <v>175</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D325" t="s">
         <v>144</v>
@@ -6099,7 +6099,7 @@
         <v>175</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C326" s="6">
         <v>15.58</v>
@@ -6979,13 +6979,13 @@
         <v>181</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C393" s="6">
         <v>14.5</v>
       </c>
       <c r="D393" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
@@ -7368,7 +7368,7 @@
         <v>181</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C421" s="6">
         <v>15.99</v>
@@ -7382,7 +7382,7 @@
         <v>181</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C422" s="6">
         <v>29.99</v>
@@ -7396,7 +7396,7 @@
         <v>181</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C423" s="6">
         <v>16.989999999999998</v>
@@ -7410,7 +7410,7 @@
         <v>181</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C424" s="6">
         <v>29.99</v>
@@ -8112,7 +8112,7 @@
         <v>181</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C475" s="6">
         <v>110</v>
@@ -8126,7 +8126,7 @@
         <v>181</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C476" s="6">
         <v>98.45</v>
@@ -8140,7 +8140,7 @@
         <v>181</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C477" s="6">
         <v>139</v>
@@ -8154,7 +8154,7 @@
         <v>181</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C478" s="6">
         <v>199</v>
@@ -8168,7 +8168,7 @@
         <v>181</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C479" s="6">
         <v>169.99</v>
@@ -8182,7 +8182,7 @@
         <v>181</v>
       </c>
       <c r="B480" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C480" s="6">
         <v>239.08</v>
@@ -8196,7 +8196,7 @@
         <v>181</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C481" s="6">
         <v>219</v>
@@ -8210,7 +8210,7 @@
         <v>181</v>
       </c>
       <c r="B482" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C482" s="6">
         <v>189.99</v>
@@ -8224,7 +8224,7 @@
         <v>181</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C483" s="6">
         <v>248</v>
@@ -8238,7 +8238,7 @@
         <v>181</v>
       </c>
       <c r="B484" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C484" s="6">
         <v>297</v>
@@ -8252,7 +8252,7 @@
         <v>181</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C485" s="6">
         <v>322</v>
@@ -9107,13 +9107,13 @@
         <v>232</v>
       </c>
       <c r="B563" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C563" s="6">
         <v>5.75</v>
       </c>
       <c r="D563" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.25">
@@ -9121,13 +9121,13 @@
         <v>232</v>
       </c>
       <c r="B564" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C564" s="6">
         <v>20</v>
       </c>
       <c r="D564" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.25">
@@ -9135,13 +9135,13 @@
         <v>232</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C565" s="6">
         <v>12.5</v>
       </c>
       <c r="D565" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.25">
@@ -9149,13 +9149,13 @@
         <v>232</v>
       </c>
       <c r="B566" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C566" s="6">
         <v>77.5</v>
       </c>
       <c r="D566" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.25">
@@ -9163,13 +9163,13 @@
         <v>232</v>
       </c>
       <c r="B567" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C567" s="6">
         <v>195</v>
       </c>
       <c r="D567" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.25">
@@ -9191,13 +9191,13 @@
         <v>276</v>
       </c>
       <c r="B572" s="3" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="C572" s="6">
-        <v>106.14</v>
+        <v>41.99</v>
       </c>
       <c r="D572" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.25">
@@ -9205,13 +9205,13 @@
         <v>276</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="C573" s="6">
-        <v>41.99</v>
+        <v>82</v>
       </c>
       <c r="D573" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.25">
@@ -9219,10 +9219,10 @@
         <v>276</v>
       </c>
       <c r="B574" s="3" t="s">
-        <v>58</v>
+        <v>256</v>
       </c>
       <c r="C574" s="6">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="D574" t="s">
         <v>145</v>
@@ -9233,13 +9233,13 @@
         <v>276</v>
       </c>
       <c r="B575" s="3" t="s">
-        <v>256</v>
+        <v>112</v>
       </c>
       <c r="C575" s="6">
-        <v>28</v>
+        <v>28.05</v>
       </c>
       <c r="D575" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.25">
@@ -9247,7 +9247,7 @@
         <v>276</v>
       </c>
       <c r="B576" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C576" s="6">
         <v>28.05</v>
@@ -9261,7 +9261,7 @@
         <v>276</v>
       </c>
       <c r="B577" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C577" s="6">
         <v>28.05</v>
@@ -9275,27 +9275,27 @@
         <v>276</v>
       </c>
       <c r="B578" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C578" s="6">
-        <v>28.05</v>
+        <v>11.2</v>
       </c>
       <c r="D578" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A579" t="s">
-        <v>276</v>
-      </c>
-      <c r="B579" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C579" s="6">
-        <v>11.2</v>
-      </c>
-      <c r="D579" t="s">
-        <v>152</v>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A581" t="s">
+        <v>144</v>
+      </c>
+      <c r="B581" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C581" s="6">
+        <v>29.87</v>
+      </c>
+      <c r="D581" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.25">
@@ -9303,13 +9303,13 @@
         <v>144</v>
       </c>
       <c r="B582" s="3" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C582" s="6">
-        <v>29.87</v>
+        <v>199</v>
       </c>
       <c r="D582" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.25">
@@ -9317,13 +9317,13 @@
         <v>144</v>
       </c>
       <c r="B583" s="3" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C583" s="6">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="D583" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.25">
@@ -9331,10 +9331,10 @@
         <v>144</v>
       </c>
       <c r="B584" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C584" s="6">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D584" t="s">
         <v>142</v>
@@ -9345,10 +9345,10 @@
         <v>144</v>
       </c>
       <c r="B585" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C585" s="6">
-        <v>189</v>
+        <v>309</v>
       </c>
       <c r="D585" t="s">
         <v>142</v>
@@ -9359,13 +9359,13 @@
         <v>144</v>
       </c>
       <c r="B586" s="3" t="s">
-        <v>31</v>
+        <v>212</v>
       </c>
       <c r="C586" s="6">
-        <v>309</v>
+        <v>175</v>
       </c>
       <c r="D586" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.25">
@@ -9373,10 +9373,10 @@
         <v>144</v>
       </c>
       <c r="B587" s="3" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="C587" s="6">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="D587" t="s">
         <v>144</v>
@@ -9387,13 +9387,13 @@
         <v>144</v>
       </c>
       <c r="B588" s="3" t="s">
-        <v>202</v>
+        <v>57</v>
       </c>
       <c r="C588" s="6">
-        <v>134</v>
+        <v>59.99</v>
       </c>
       <c r="D588" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.25">
@@ -9401,10 +9401,10 @@
         <v>144</v>
       </c>
       <c r="B589" s="3" t="s">
-        <v>57</v>
+        <v>256</v>
       </c>
       <c r="C589" s="6">
-        <v>59.99</v>
+        <v>32.99</v>
       </c>
       <c r="D589" t="s">
         <v>145</v>
@@ -9415,10 +9415,10 @@
         <v>144</v>
       </c>
       <c r="B590" s="3" t="s">
-        <v>256</v>
+        <v>58</v>
       </c>
       <c r="C590" s="6">
-        <v>32.99</v>
+        <v>129</v>
       </c>
       <c r="D590" t="s">
         <v>145</v>
@@ -9429,10 +9429,10 @@
         <v>144</v>
       </c>
       <c r="B591" s="3" t="s">
-        <v>58</v>
+        <v>257</v>
       </c>
       <c r="C591" s="6">
-        <v>129</v>
+        <v>149.99</v>
       </c>
       <c r="D591" t="s">
         <v>145</v>
@@ -9443,13 +9443,13 @@
         <v>144</v>
       </c>
       <c r="B592" s="3" t="s">
-        <v>257</v>
+        <v>59</v>
       </c>
       <c r="C592" s="6">
-        <v>149.99</v>
+        <v>47.99</v>
       </c>
       <c r="D592" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.25">
@@ -9457,10 +9457,10 @@
         <v>144</v>
       </c>
       <c r="B593" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C593" s="6">
-        <v>47.99</v>
+        <v>39.99</v>
       </c>
       <c r="D593" t="s">
         <v>146</v>
@@ -9471,13 +9471,13 @@
         <v>144</v>
       </c>
       <c r="B594" s="3" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="C594" s="6">
         <v>39.99</v>
       </c>
       <c r="D594" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.25">
@@ -9485,10 +9485,7 @@
         <v>144</v>
       </c>
       <c r="B595" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C595" s="6">
-        <v>39.99</v>
+        <v>106</v>
       </c>
       <c r="D595" t="s">
         <v>151</v>
@@ -9499,24 +9496,27 @@
         <v>144</v>
       </c>
       <c r="B596" s="3" t="s">
-        <v>106</v>
+        <v>278</v>
+      </c>
+      <c r="C596" s="6">
+        <v>36.950000000000003</v>
       </c>
       <c r="D596" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A597" t="s">
-        <v>144</v>
-      </c>
-      <c r="B597" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C597" s="6">
-        <v>36.950000000000003</v>
-      </c>
-      <c r="D597" t="s">
         <v>173</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A599" t="s">
+        <v>288</v>
+      </c>
+      <c r="B599" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C599" s="6">
+        <v>18</v>
+      </c>
+      <c r="D599" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.25">
@@ -9524,10 +9524,10 @@
         <v>288</v>
       </c>
       <c r="B600" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C600" s="6">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="D600" t="s">
         <v>139</v>
@@ -9538,10 +9538,10 @@
         <v>288</v>
       </c>
       <c r="B601" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C601" s="6">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D601" t="s">
         <v>139</v>
@@ -9552,10 +9552,10 @@
         <v>288</v>
       </c>
       <c r="B602" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C602" s="6">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="D602" t="s">
         <v>139</v>
@@ -9566,10 +9566,10 @@
         <v>288</v>
       </c>
       <c r="B603" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C603" s="6">
-        <v>134</v>
+        <v>185</v>
       </c>
       <c r="D603" t="s">
         <v>139</v>
@@ -9580,10 +9580,10 @@
         <v>288</v>
       </c>
       <c r="B604" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C604" s="6">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="D604" t="s">
         <v>139</v>
@@ -9594,10 +9594,10 @@
         <v>288</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C605" s="6">
-        <v>155</v>
+        <v>239</v>
       </c>
       <c r="D605" t="s">
         <v>139</v>
@@ -9608,10 +9608,10 @@
         <v>288</v>
       </c>
       <c r="B606" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C606" s="6">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="D606" t="s">
         <v>139</v>
@@ -9622,10 +9622,10 @@
         <v>288</v>
       </c>
       <c r="B607" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C607" s="6">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="D607" t="s">
         <v>139</v>
@@ -9636,10 +9636,10 @@
         <v>288</v>
       </c>
       <c r="B608" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C608" s="6">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="D608" t="s">
         <v>139</v>
@@ -9650,10 +9650,10 @@
         <v>288</v>
       </c>
       <c r="B609" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C609" s="6">
-        <v>210</v>
+        <v>285</v>
       </c>
       <c r="D609" t="s">
         <v>139</v>
@@ -9664,10 +9664,10 @@
         <v>288</v>
       </c>
       <c r="B610" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C610" s="6">
-        <v>285</v>
+        <v>250</v>
       </c>
       <c r="D610" t="s">
         <v>139</v>
@@ -9678,13 +9678,13 @@
         <v>288</v>
       </c>
       <c r="B611" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C611" s="6">
-        <v>250</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D611" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.25">
@@ -9692,10 +9692,10 @@
         <v>288</v>
       </c>
       <c r="B612" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C612" s="6">
-        <v>19.989999999999998</v>
+        <v>29.99</v>
       </c>
       <c r="D612" t="s">
         <v>140</v>
@@ -9706,13 +9706,13 @@
         <v>288</v>
       </c>
       <c r="B613" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C613" s="6">
-        <v>29.99</v>
+        <v>155</v>
       </c>
       <c r="D613" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.25">
@@ -9720,10 +9720,10 @@
         <v>288</v>
       </c>
       <c r="B614" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C614" s="6">
-        <v>155</v>
+        <v>190</v>
       </c>
       <c r="D614" t="s">
         <v>142</v>
@@ -9734,10 +9734,10 @@
         <v>288</v>
       </c>
       <c r="B615" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C615" s="6">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D615" t="s">
         <v>142</v>
@@ -9748,10 +9748,10 @@
         <v>288</v>
       </c>
       <c r="B616" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C616" s="6">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D616" t="s">
         <v>142</v>
@@ -9762,10 +9762,10 @@
         <v>288</v>
       </c>
       <c r="B617" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C617" s="6">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="D617" t="s">
         <v>142</v>
@@ -9776,10 +9776,10 @@
         <v>288</v>
       </c>
       <c r="B618" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C618" s="6">
-        <v>199</v>
+        <v>260</v>
       </c>
       <c r="D618" t="s">
         <v>142</v>
@@ -9790,10 +9790,10 @@
         <v>288</v>
       </c>
       <c r="B619" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C619" s="6">
-        <v>260</v>
+        <v>389</v>
       </c>
       <c r="D619" t="s">
         <v>142</v>
@@ -9804,10 +9804,10 @@
         <v>288</v>
       </c>
       <c r="B620" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C620" s="6">
-        <v>389</v>
+        <v>399.99</v>
       </c>
       <c r="D620" t="s">
         <v>142</v>
@@ -9818,10 +9818,10 @@
         <v>288</v>
       </c>
       <c r="B621" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C621" s="6">
-        <v>399.99</v>
+        <v>89.23</v>
       </c>
       <c r="D621" t="s">
         <v>142</v>
@@ -9831,28 +9831,28 @@
       <c r="A622" t="s">
         <v>288</v>
       </c>
-      <c r="B622" s="3" t="s">
-        <v>37</v>
+      <c r="B622" s="3">
+        <v>6102</v>
       </c>
       <c r="C622" s="6">
-        <v>89.23</v>
+        <v>44</v>
       </c>
       <c r="D622" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>288</v>
       </c>
-      <c r="B623" s="3">
-        <v>6102</v>
+      <c r="B623" s="3" t="s">
+        <v>281</v>
       </c>
       <c r="C623" s="6">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D623" t="s">
-        <v>144</v>
+        <v>269</v>
       </c>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.25">
@@ -9860,10 +9860,10 @@
         <v>288</v>
       </c>
       <c r="B624" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C624" s="6">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D624" t="s">
         <v>269</v>
@@ -9874,10 +9874,10 @@
         <v>288</v>
       </c>
       <c r="B625" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C625" s="6">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D625" t="s">
         <v>269</v>
@@ -9888,10 +9888,10 @@
         <v>288</v>
       </c>
       <c r="B626" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C626" s="6">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D626" t="s">
         <v>269</v>
@@ -9902,10 +9902,10 @@
         <v>288</v>
       </c>
       <c r="B627" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C627" s="6">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="D627" t="s">
         <v>269</v>
@@ -9916,10 +9916,10 @@
         <v>288</v>
       </c>
       <c r="B628" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C628" s="6">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="D628" t="s">
         <v>269</v>
@@ -9930,13 +9930,13 @@
         <v>288</v>
       </c>
       <c r="B629" s="3" t="s">
-        <v>286</v>
+        <v>55</v>
       </c>
       <c r="C629" s="6">
-        <v>114</v>
+        <v>27.99</v>
       </c>
       <c r="D629" t="s">
-        <v>269</v>
+        <v>145</v>
       </c>
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.25">
@@ -9944,10 +9944,10 @@
         <v>288</v>
       </c>
       <c r="B630" s="3" t="s">
-        <v>55</v>
+        <v>255</v>
       </c>
       <c r="C630" s="6">
-        <v>27.99</v>
+        <v>28.99</v>
       </c>
       <c r="D630" t="s">
         <v>145</v>
@@ -9958,10 +9958,10 @@
         <v>288</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>255</v>
+        <v>56</v>
       </c>
       <c r="C631" s="6">
-        <v>28.99</v>
+        <v>39.99</v>
       </c>
       <c r="D631" t="s">
         <v>145</v>
@@ -9972,10 +9972,10 @@
         <v>288</v>
       </c>
       <c r="B632" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C632" s="6">
-        <v>39.99</v>
+        <v>58</v>
       </c>
       <c r="D632" t="s">
         <v>145</v>
@@ -9986,10 +9986,10 @@
         <v>288</v>
       </c>
       <c r="B633" s="3" t="s">
-        <v>57</v>
+        <v>256</v>
       </c>
       <c r="C633" s="6">
-        <v>58</v>
+        <v>42.99</v>
       </c>
       <c r="D633" t="s">
         <v>145</v>
@@ -10000,10 +10000,10 @@
         <v>288</v>
       </c>
       <c r="B634" s="3" t="s">
-        <v>256</v>
+        <v>58</v>
       </c>
       <c r="C634" s="6">
-        <v>42.99</v>
+        <v>129</v>
       </c>
       <c r="D634" t="s">
         <v>145</v>
@@ -10014,10 +10014,10 @@
         <v>288</v>
       </c>
       <c r="B635" s="3" t="s">
-        <v>58</v>
+        <v>257</v>
       </c>
       <c r="C635" s="6">
-        <v>129</v>
+        <v>180</v>
       </c>
       <c r="D635" t="s">
         <v>145</v>
@@ -10028,13 +10028,13 @@
         <v>288</v>
       </c>
       <c r="B636" s="3" t="s">
-        <v>257</v>
+        <v>59</v>
       </c>
       <c r="C636" s="6">
-        <v>180</v>
+        <v>54.5</v>
       </c>
       <c r="D636" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.25">
@@ -10042,10 +10042,10 @@
         <v>288</v>
       </c>
       <c r="B637" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C637" s="6">
-        <v>54.5</v>
+        <v>48.99</v>
       </c>
       <c r="D637" t="s">
         <v>146</v>
@@ -10056,10 +10056,10 @@
         <v>288</v>
       </c>
       <c r="B638" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C638" s="6">
-        <v>48.99</v>
+        <v>39.99</v>
       </c>
       <c r="D638" t="s">
         <v>146</v>
@@ -10070,10 +10070,10 @@
         <v>288</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C639" s="6">
-        <v>39.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="D639" t="s">
         <v>146</v>
@@ -10084,10 +10084,10 @@
         <v>288</v>
       </c>
       <c r="B640" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C640" s="6">
-        <v>64.989999999999995</v>
+        <v>29.99</v>
       </c>
       <c r="D640" t="s">
         <v>146</v>
@@ -10098,10 +10098,10 @@
         <v>288</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C641" s="6">
-        <v>29.99</v>
+        <v>28.99</v>
       </c>
       <c r="D641" t="s">
         <v>146</v>
@@ -10112,10 +10112,7 @@
         <v>288</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C642" s="6">
-        <v>28.99</v>
+        <v>176</v>
       </c>
       <c r="D642" t="s">
         <v>146</v>
@@ -10126,7 +10123,10 @@
         <v>288</v>
       </c>
       <c r="B643" s="3" t="s">
-        <v>176</v>
+        <v>62</v>
+      </c>
+      <c r="C643" s="6">
+        <v>29.99</v>
       </c>
       <c r="D643" t="s">
         <v>146</v>
@@ -10137,10 +10137,10 @@
         <v>288</v>
       </c>
       <c r="B644" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C644" s="6">
-        <v>29.99</v>
+        <v>25.99</v>
       </c>
       <c r="D644" t="s">
         <v>146</v>
@@ -10150,28 +10150,28 @@
       <c r="A645" t="s">
         <v>288</v>
       </c>
-      <c r="B645" s="3" t="s">
-        <v>65</v>
+      <c r="B645" s="3">
+        <v>6642</v>
       </c>
       <c r="C645" s="6">
-        <v>25.99</v>
+        <v>50</v>
       </c>
       <c r="D645" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>288</v>
       </c>
-      <c r="B646" s="3">
-        <v>6642</v>
+      <c r="B646" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="C646" s="6">
-        <v>50</v>
+        <v>19.2</v>
       </c>
       <c r="D646" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.25">
@@ -10207,10 +10207,10 @@
         <v>288</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C649" s="6">
-        <v>39.99</v>
+        <v>30.58</v>
       </c>
       <c r="D649" t="s">
         <v>154</v>
@@ -10221,27 +10221,27 @@
         <v>288</v>
       </c>
       <c r="B650" s="3" t="s">
-        <v>287</v>
+        <v>127</v>
       </c>
       <c r="C650" s="6">
-        <v>90</v>
+        <v>39.99</v>
       </c>
       <c r="D650" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A653" t="s">
-        <v>290</v>
-      </c>
-      <c r="B653" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C653" s="6">
-        <v>42.75</v>
-      </c>
-      <c r="D653" t="s">
-        <v>139</v>
+    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A651" t="s">
+        <v>288</v>
+      </c>
+      <c r="B651" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C651" s="6">
+        <v>90</v>
+      </c>
+      <c r="D651" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.25">
@@ -10249,10 +10249,10 @@
         <v>290</v>
       </c>
       <c r="B654" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C654" s="6">
-        <v>68</v>
+        <v>42.75</v>
       </c>
       <c r="D654" t="s">
         <v>139</v>
@@ -10263,35 +10263,38 @@
         <v>290</v>
       </c>
       <c r="B655" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C655" s="6">
-        <v>82.2</v>
+        <v>68</v>
       </c>
       <c r="D655" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A657" t="s">
-        <v>303</v>
-      </c>
-      <c r="B657" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C657" s="6">
-        <v>10</v>
-      </c>
-      <c r="D657" t="s">
-        <v>140</v>
+    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A656" t="s">
+        <v>290</v>
+      </c>
+      <c r="B656" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C656" s="6">
+        <v>82.2</v>
+      </c>
+      <c r="D656" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B658" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="C658" s="6">
+        <v>10</v>
       </c>
       <c r="D658" t="s">
         <v>140</v>
@@ -10299,27 +10302,24 @@
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>303</v>
-      </c>
-      <c r="B659" s="3">
-        <v>4642</v>
-      </c>
-      <c r="C659" s="6">
-        <v>18.96</v>
+        <v>304</v>
+      </c>
+      <c r="B659" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D659" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B660" s="3">
-        <v>6642</v>
+        <v>4642</v>
       </c>
       <c r="C660" s="6">
-        <v>22.37</v>
+        <v>18.96</v>
       </c>
       <c r="D660" t="s">
         <v>148</v>
@@ -10327,24 +10327,24 @@
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>303</v>
-      </c>
-      <c r="B661" s="3" t="s">
-        <v>116</v>
+        <v>304</v>
+      </c>
+      <c r="B661" s="3">
+        <v>6642</v>
       </c>
       <c r="C661" s="6">
-        <v>9.1</v>
+        <v>22.37</v>
       </c>
       <c r="D661" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B662" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C662" s="6">
         <v>9.1</v>
@@ -10353,26 +10353,26 @@
         <v>152</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A667" t="s">
-        <v>338</v>
-      </c>
-      <c r="B667" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C667" s="6">
-        <v>5</v>
-      </c>
-      <c r="D667" t="s">
-        <v>140</v>
+    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A663" t="s">
+        <v>304</v>
+      </c>
+      <c r="B663" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C663" s="6">
+        <v>9.1</v>
+      </c>
+      <c r="D663" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>338</v>
+        <v>292</v>
       </c>
       <c r="B668" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C668" s="6">
         <v>5</v>
@@ -10381,93 +10381,93 @@
         <v>140</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A672" t="s">
+    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A669" t="s">
         <v>292</v>
       </c>
-      <c r="B672" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C672" s="6">
-        <v>3.15</v>
-      </c>
-      <c r="D672" t="s">
-        <v>302</v>
+      <c r="B669" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C669" s="6">
+        <v>5</v>
+      </c>
+      <c r="D669" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B673" s="3" t="s">
         <v>295</v>
       </c>
       <c r="C673" s="6">
-        <v>7.65</v>
+        <v>3.15</v>
       </c>
       <c r="D673" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B674" s="3" t="s">
         <v>296</v>
       </c>
       <c r="C674" s="6">
-        <v>8.1</v>
+        <v>7.65</v>
       </c>
       <c r="D674" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B675" s="3" t="s">
         <v>297</v>
       </c>
       <c r="C675" s="6">
-        <v>10.8</v>
+        <v>8.1</v>
       </c>
       <c r="D675" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B676" s="3" t="s">
         <v>298</v>
       </c>
       <c r="C676" s="6">
-        <v>12.2</v>
+        <v>10.8</v>
       </c>
       <c r="D676" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B677" s="3" t="s">
         <v>299</v>
       </c>
       <c r="C677" s="6">
-        <v>11.25</v>
+        <v>12.2</v>
       </c>
       <c r="D677" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B678" s="3" t="s">
         <v>300</v>
@@ -10476,12 +10476,12 @@
         <v>11.25</v>
       </c>
       <c r="D678" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B679" s="3" t="s">
         <v>301</v>
@@ -10490,96 +10490,96 @@
         <v>11.25</v>
       </c>
       <c r="D679" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A680" t="s">
+        <v>293</v>
+      </c>
+      <c r="B680" s="3" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A682" t="s">
-        <v>293</v>
-      </c>
-      <c r="B682" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C682" s="6">
-        <v>3.36</v>
-      </c>
-      <c r="D682" t="s">
-        <v>302</v>
+      <c r="C680" s="6">
+        <v>11.25</v>
+      </c>
+      <c r="D680" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B683" s="3" t="s">
         <v>295</v>
       </c>
       <c r="C683" s="6">
-        <v>10.19</v>
+        <v>3.36</v>
       </c>
       <c r="D683" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="684" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B684" s="3" t="s">
         <v>296</v>
       </c>
       <c r="C684" s="6">
-        <v>14.4</v>
+        <v>10.19</v>
       </c>
       <c r="D684" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="685" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B685" s="3" t="s">
         <v>297</v>
       </c>
       <c r="C685" s="6">
-        <v>14.39</v>
+        <v>14.4</v>
       </c>
       <c r="D685" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="686" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B686" s="3" t="s">
         <v>298</v>
       </c>
       <c r="C686" s="6">
-        <v>11.52</v>
+        <v>14.39</v>
       </c>
       <c r="D686" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B687" s="3" t="s">
         <v>299</v>
       </c>
       <c r="C687" s="6">
-        <v>12</v>
+        <v>11.52</v>
       </c>
       <c r="D687" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B688" s="3" t="s">
         <v>300</v>
@@ -10588,12 +10588,12 @@
         <v>12</v>
       </c>
       <c r="D688" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B689" s="3" t="s">
         <v>301</v>
@@ -10602,7 +10602,21 @@
         <v>12</v>
       </c>
       <c r="D689" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="690" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A690" t="s">
+        <v>294</v>
+      </c>
+      <c r="B690" s="3" t="s">
         <v>302</v>
+      </c>
+      <c r="C690" s="6">
+        <v>12</v>
+      </c>
+      <c r="D690" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>

--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Garretts Reports\Sales Report App\Excell Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E33625B-0341-46EF-A6E9-CF33ACABBEA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882D510E-3A6F-43A8-9910-B5C6E65588EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21150" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1895" uniqueCount="339">
   <si>
     <t>BGC10</t>
   </si>
@@ -1439,7 +1439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6055176-08B8-4018-B9DF-7F26AB5DB49D}">
-  <dimension ref="A1:K690"/>
+  <dimension ref="A1:K692"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -9345,10 +9345,10 @@
         <v>144</v>
       </c>
       <c r="B585" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C585" s="6">
-        <v>309</v>
+        <v>224.1</v>
       </c>
       <c r="D585" t="s">
         <v>142</v>
@@ -9359,24 +9359,24 @@
         <v>144</v>
       </c>
       <c r="B586" s="3" t="s">
-        <v>212</v>
+        <v>31</v>
       </c>
       <c r="C586" s="6">
-        <v>175</v>
+        <v>309</v>
       </c>
       <c r="D586" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>144</v>
       </c>
-      <c r="B587" s="3" t="s">
-        <v>202</v>
+      <c r="B587" s="3">
+        <v>6102</v>
       </c>
       <c r="C587" s="6">
-        <v>134</v>
+        <v>38.99</v>
       </c>
       <c r="D587" t="s">
         <v>144</v>
@@ -9387,13 +9387,13 @@
         <v>144</v>
       </c>
       <c r="B588" s="3" t="s">
-        <v>57</v>
+        <v>212</v>
       </c>
       <c r="C588" s="6">
-        <v>59.99</v>
+        <v>175</v>
       </c>
       <c r="D588" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.25">
@@ -9401,13 +9401,13 @@
         <v>144</v>
       </c>
       <c r="B589" s="3" t="s">
-        <v>256</v>
+        <v>202</v>
       </c>
       <c r="C589" s="6">
-        <v>32.99</v>
+        <v>134</v>
       </c>
       <c r="D589" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.25">
@@ -9415,10 +9415,10 @@
         <v>144</v>
       </c>
       <c r="B590" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C590" s="6">
-        <v>129</v>
+        <v>59.99</v>
       </c>
       <c r="D590" t="s">
         <v>145</v>
@@ -9429,10 +9429,10 @@
         <v>144</v>
       </c>
       <c r="B591" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C591" s="6">
-        <v>149.99</v>
+        <v>32.99</v>
       </c>
       <c r="D591" t="s">
         <v>145</v>
@@ -9443,13 +9443,13 @@
         <v>144</v>
       </c>
       <c r="B592" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C592" s="6">
-        <v>47.99</v>
+        <v>129</v>
       </c>
       <c r="D592" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.25">
@@ -9457,13 +9457,13 @@
         <v>144</v>
       </c>
       <c r="B593" s="3" t="s">
-        <v>64</v>
+        <v>257</v>
       </c>
       <c r="C593" s="6">
-        <v>39.99</v>
+        <v>149.99</v>
       </c>
       <c r="D593" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.25">
@@ -9471,13 +9471,13 @@
         <v>144</v>
       </c>
       <c r="B594" s="3" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="C594" s="6">
-        <v>39.99</v>
+        <v>47.99</v>
       </c>
       <c r="D594" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.25">
@@ -9485,10 +9485,13 @@
         <v>144</v>
       </c>
       <c r="B595" s="3" t="s">
-        <v>106</v>
+        <v>64</v>
+      </c>
+      <c r="C595" s="6">
+        <v>39.99</v>
       </c>
       <c r="D595" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.25">
@@ -9496,41 +9499,38 @@
         <v>144</v>
       </c>
       <c r="B596" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C596" s="6">
+        <v>39.99</v>
+      </c>
+      <c r="D596" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A597" t="s">
+        <v>144</v>
+      </c>
+      <c r="B597" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D597" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A598" t="s">
+        <v>144</v>
+      </c>
+      <c r="B598" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="C596" s="6">
+      <c r="C598" s="6">
         <v>36.950000000000003</v>
       </c>
-      <c r="D596" t="s">
+      <c r="D598" t="s">
         <v>173</v>
-      </c>
-    </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A599" t="s">
-        <v>288</v>
-      </c>
-      <c r="B599" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C599" s="6">
-        <v>18</v>
-      </c>
-      <c r="D599" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A600" t="s">
-        <v>288</v>
-      </c>
-      <c r="B600" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C600" s="6">
-        <v>100</v>
-      </c>
-      <c r="D600" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.25">
@@ -9538,10 +9538,10 @@
         <v>288</v>
       </c>
       <c r="B601" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C601" s="6">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="D601" t="s">
         <v>139</v>
@@ -9552,10 +9552,10 @@
         <v>288</v>
       </c>
       <c r="B602" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C602" s="6">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="D602" t="s">
         <v>139</v>
@@ -9566,10 +9566,10 @@
         <v>288</v>
       </c>
       <c r="B603" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C603" s="6">
-        <v>185</v>
+        <v>99</v>
       </c>
       <c r="D603" t="s">
         <v>139</v>
@@ -9580,10 +9580,10 @@
         <v>288</v>
       </c>
       <c r="B604" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C604" s="6">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="D604" t="s">
         <v>139</v>
@@ -9594,10 +9594,10 @@
         <v>288</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C605" s="6">
-        <v>239</v>
+        <v>185</v>
       </c>
       <c r="D605" t="s">
         <v>139</v>
@@ -9608,10 +9608,10 @@
         <v>288</v>
       </c>
       <c r="B606" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C606" s="6">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="D606" t="s">
         <v>139</v>
@@ -9622,10 +9622,10 @@
         <v>288</v>
       </c>
       <c r="B607" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C607" s="6">
-        <v>189</v>
+        <v>239</v>
       </c>
       <c r="D607" t="s">
         <v>139</v>
@@ -9636,10 +9636,10 @@
         <v>288</v>
       </c>
       <c r="B608" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C608" s="6">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D608" t="s">
         <v>139</v>
@@ -9650,10 +9650,10 @@
         <v>288</v>
       </c>
       <c r="B609" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C609" s="6">
-        <v>285</v>
+        <v>189</v>
       </c>
       <c r="D609" t="s">
         <v>139</v>
@@ -9664,10 +9664,10 @@
         <v>288</v>
       </c>
       <c r="B610" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C610" s="6">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="D610" t="s">
         <v>139</v>
@@ -9678,13 +9678,13 @@
         <v>288</v>
       </c>
       <c r="B611" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C611" s="6">
-        <v>19.989999999999998</v>
+        <v>285</v>
       </c>
       <c r="D611" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.25">
@@ -9692,13 +9692,13 @@
         <v>288</v>
       </c>
       <c r="B612" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C612" s="6">
-        <v>29.99</v>
+        <v>250</v>
       </c>
       <c r="D612" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.25">
@@ -9706,13 +9706,13 @@
         <v>288</v>
       </c>
       <c r="B613" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C613" s="6">
-        <v>155</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D613" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.25">
@@ -9720,13 +9720,13 @@
         <v>288</v>
       </c>
       <c r="B614" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C614" s="6">
-        <v>190</v>
+        <v>29.99</v>
       </c>
       <c r="D614" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.25">
@@ -9734,10 +9734,10 @@
         <v>288</v>
       </c>
       <c r="B615" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C615" s="6">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="D615" t="s">
         <v>142</v>
@@ -9748,10 +9748,10 @@
         <v>288</v>
       </c>
       <c r="B616" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C616" s="6">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="D616" t="s">
         <v>142</v>
@@ -9762,10 +9762,10 @@
         <v>288</v>
       </c>
       <c r="B617" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C617" s="6">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="D617" t="s">
         <v>142</v>
@@ -9776,10 +9776,10 @@
         <v>288</v>
       </c>
       <c r="B618" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C618" s="6">
-        <v>260</v>
+        <v>170</v>
       </c>
       <c r="D618" t="s">
         <v>142</v>
@@ -9790,10 +9790,10 @@
         <v>288</v>
       </c>
       <c r="B619" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C619" s="6">
-        <v>389</v>
+        <v>199</v>
       </c>
       <c r="D619" t="s">
         <v>142</v>
@@ -9804,10 +9804,10 @@
         <v>288</v>
       </c>
       <c r="B620" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C620" s="6">
-        <v>399.99</v>
+        <v>260</v>
       </c>
       <c r="D620" t="s">
         <v>142</v>
@@ -9818,10 +9818,10 @@
         <v>288</v>
       </c>
       <c r="B621" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C621" s="6">
-        <v>89.23</v>
+        <v>389</v>
       </c>
       <c r="D621" t="s">
         <v>142</v>
@@ -9831,14 +9831,14 @@
       <c r="A622" t="s">
         <v>288</v>
       </c>
-      <c r="B622" s="3">
-        <v>6102</v>
+      <c r="B622" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="C622" s="6">
-        <v>44</v>
+        <v>399.99</v>
       </c>
       <c r="D622" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.25">
@@ -9846,27 +9846,27 @@
         <v>288</v>
       </c>
       <c r="B623" s="3" t="s">
-        <v>281</v>
+        <v>37</v>
       </c>
       <c r="C623" s="6">
-        <v>64</v>
+        <v>89.23</v>
       </c>
       <c r="D623" t="s">
-        <v>269</v>
+        <v>142</v>
       </c>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>288</v>
       </c>
-      <c r="B624" s="3" t="s">
-        <v>282</v>
+      <c r="B624" s="3">
+        <v>6102</v>
       </c>
       <c r="C624" s="6">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="D624" t="s">
-        <v>269</v>
+        <v>144</v>
       </c>
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.25">
@@ -9874,10 +9874,10 @@
         <v>288</v>
       </c>
       <c r="B625" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C625" s="6">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D625" t="s">
         <v>269</v>
@@ -9888,10 +9888,10 @@
         <v>288</v>
       </c>
       <c r="B626" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C626" s="6">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D626" t="s">
         <v>269</v>
@@ -9902,10 +9902,10 @@
         <v>288</v>
       </c>
       <c r="B627" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C627" s="6">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D627" t="s">
         <v>269</v>
@@ -9916,10 +9916,10 @@
         <v>288</v>
       </c>
       <c r="B628" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C628" s="6">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="D628" t="s">
         <v>269</v>
@@ -9930,13 +9930,13 @@
         <v>288</v>
       </c>
       <c r="B629" s="3" t="s">
-        <v>55</v>
+        <v>285</v>
       </c>
       <c r="C629" s="6">
-        <v>27.99</v>
+        <v>90</v>
       </c>
       <c r="D629" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.25">
@@ -9944,13 +9944,13 @@
         <v>288</v>
       </c>
       <c r="B630" s="3" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="C630" s="6">
-        <v>28.99</v>
+        <v>114</v>
       </c>
       <c r="D630" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.25">
@@ -9958,10 +9958,10 @@
         <v>288</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C631" s="6">
-        <v>39.99</v>
+        <v>27.99</v>
       </c>
       <c r="D631" t="s">
         <v>145</v>
@@ -9972,10 +9972,10 @@
         <v>288</v>
       </c>
       <c r="B632" s="3" t="s">
-        <v>57</v>
+        <v>255</v>
       </c>
       <c r="C632" s="6">
-        <v>58</v>
+        <v>28.99</v>
       </c>
       <c r="D632" t="s">
         <v>145</v>
@@ -9986,10 +9986,10 @@
         <v>288</v>
       </c>
       <c r="B633" s="3" t="s">
-        <v>256</v>
+        <v>56</v>
       </c>
       <c r="C633" s="6">
-        <v>42.99</v>
+        <v>39.99</v>
       </c>
       <c r="D633" t="s">
         <v>145</v>
@@ -10000,10 +10000,10 @@
         <v>288</v>
       </c>
       <c r="B634" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C634" s="6">
         <v>58</v>
-      </c>
-      <c r="C634" s="6">
-        <v>129</v>
       </c>
       <c r="D634" t="s">
         <v>145</v>
@@ -10014,10 +10014,10 @@
         <v>288</v>
       </c>
       <c r="B635" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C635" s="6">
-        <v>180</v>
+        <v>42.99</v>
       </c>
       <c r="D635" t="s">
         <v>145</v>
@@ -10028,13 +10028,13 @@
         <v>288</v>
       </c>
       <c r="B636" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C636" s="6">
-        <v>54.5</v>
+        <v>129</v>
       </c>
       <c r="D636" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.25">
@@ -10042,13 +10042,13 @@
         <v>288</v>
       </c>
       <c r="B637" s="3" t="s">
-        <v>64</v>
+        <v>257</v>
       </c>
       <c r="C637" s="6">
-        <v>48.99</v>
+        <v>180</v>
       </c>
       <c r="D637" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.25">
@@ -10056,10 +10056,10 @@
         <v>288</v>
       </c>
       <c r="B638" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C638" s="6">
-        <v>39.99</v>
+        <v>54.5</v>
       </c>
       <c r="D638" t="s">
         <v>146</v>
@@ -10070,10 +10070,10 @@
         <v>288</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C639" s="6">
-        <v>64.989999999999995</v>
+        <v>48.99</v>
       </c>
       <c r="D639" t="s">
         <v>146</v>
@@ -10084,10 +10084,10 @@
         <v>288</v>
       </c>
       <c r="B640" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C640" s="6">
-        <v>29.99</v>
+        <v>39.99</v>
       </c>
       <c r="D640" t="s">
         <v>146</v>
@@ -10098,10 +10098,10 @@
         <v>288</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C641" s="6">
-        <v>28.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="D641" t="s">
         <v>146</v>
@@ -10112,7 +10112,10 @@
         <v>288</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>176</v>
+        <v>60</v>
+      </c>
+      <c r="C642" s="6">
+        <v>29.99</v>
       </c>
       <c r="D642" t="s">
         <v>146</v>
@@ -10123,10 +10126,10 @@
         <v>288</v>
       </c>
       <c r="B643" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C643" s="6">
-        <v>29.99</v>
+        <v>28.99</v>
       </c>
       <c r="D643" t="s">
         <v>146</v>
@@ -10137,10 +10140,7 @@
         <v>288</v>
       </c>
       <c r="B644" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C644" s="6">
-        <v>25.99</v>
+        <v>176</v>
       </c>
       <c r="D644" t="s">
         <v>146</v>
@@ -10150,14 +10150,14 @@
       <c r="A645" t="s">
         <v>288</v>
       </c>
-      <c r="B645" s="3">
-        <v>6642</v>
+      <c r="B645" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C645" s="6">
-        <v>50</v>
+        <v>29.99</v>
       </c>
       <c r="D645" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.25">
@@ -10165,27 +10165,27 @@
         <v>288</v>
       </c>
       <c r="B646" s="3" t="s">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="C646" s="6">
-        <v>19.2</v>
+        <v>25.99</v>
       </c>
       <c r="D646" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>288</v>
       </c>
-      <c r="B647" s="3" t="s">
-        <v>109</v>
+      <c r="B647" s="3">
+        <v>6642</v>
       </c>
       <c r="C647" s="6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D647" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.25">
@@ -10193,10 +10193,10 @@
         <v>288</v>
       </c>
       <c r="B648" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C648" s="6">
-        <v>40</v>
+        <v>19.2</v>
       </c>
       <c r="D648" t="s">
         <v>152</v>
@@ -10207,13 +10207,13 @@
         <v>288</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="C649" s="6">
-        <v>30.58</v>
+        <v>40</v>
       </c>
       <c r="D649" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.25">
@@ -10221,13 +10221,13 @@
         <v>288</v>
       </c>
       <c r="B650" s="3" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="C650" s="6">
-        <v>39.99</v>
+        <v>40</v>
       </c>
       <c r="D650" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.25">
@@ -10235,41 +10235,41 @@
         <v>288</v>
       </c>
       <c r="B651" s="3" t="s">
-        <v>287</v>
+        <v>130</v>
       </c>
       <c r="C651" s="6">
-        <v>90</v>
+        <v>30.58</v>
       </c>
       <c r="D651" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A654" t="s">
-        <v>290</v>
-      </c>
-      <c r="B654" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C654" s="6">
-        <v>42.75</v>
-      </c>
-      <c r="D654" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A655" t="s">
-        <v>290</v>
-      </c>
-      <c r="B655" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C655" s="6">
-        <v>68</v>
-      </c>
-      <c r="D655" t="s">
-        <v>139</v>
+    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A652" t="s">
+        <v>288</v>
+      </c>
+      <c r="B652" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C652" s="6">
+        <v>39.99</v>
+      </c>
+      <c r="D652" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A653" t="s">
+        <v>288</v>
+      </c>
+      <c r="B653" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C653" s="6">
+        <v>90</v>
+      </c>
+      <c r="D653" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.25">
@@ -10277,150 +10277,150 @@
         <v>290</v>
       </c>
       <c r="B656" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C656" s="6">
-        <v>82.2</v>
+        <v>42.75</v>
       </c>
       <c r="D656" t="s">
         <v>139</v>
       </c>
     </row>
+    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A657" t="s">
+        <v>290</v>
+      </c>
+      <c r="B657" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C657" s="6">
+        <v>68</v>
+      </c>
+      <c r="D657" t="s">
+        <v>139</v>
+      </c>
+    </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="B658" s="3" t="s">
-        <v>22</v>
+        <v>227</v>
       </c>
       <c r="C658" s="6">
-        <v>10</v>
+        <v>82.2</v>
       </c>
       <c r="D658" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A659" t="s">
-        <v>304</v>
-      </c>
-      <c r="B659" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D659" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>304</v>
       </c>
-      <c r="B660" s="3">
-        <v>4642</v>
+      <c r="B660" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="C660" s="6">
-        <v>18.96</v>
+        <v>10</v>
       </c>
       <c r="D660" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>304</v>
       </c>
-      <c r="B661" s="3">
-        <v>6642</v>
-      </c>
-      <c r="C661" s="6">
-        <v>22.37</v>
+      <c r="B661" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D661" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>304</v>
       </c>
-      <c r="B662" s="3" t="s">
-        <v>116</v>
+      <c r="B662" s="3">
+        <v>4642</v>
       </c>
       <c r="C662" s="6">
-        <v>9.1</v>
+        <v>18.96</v>
       </c>
       <c r="D662" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>304</v>
       </c>
-      <c r="B663" s="3" t="s">
+      <c r="B663" s="3">
+        <v>6642</v>
+      </c>
+      <c r="C663" s="6">
+        <v>22.37</v>
+      </c>
+      <c r="D663" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="664" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A664" t="s">
+        <v>304</v>
+      </c>
+      <c r="B664" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C664" s="6">
+        <v>9.1</v>
+      </c>
+      <c r="D664" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A665" t="s">
+        <v>304</v>
+      </c>
+      <c r="B665" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C663" s="6">
+      <c r="C665" s="6">
         <v>9.1</v>
       </c>
-      <c r="D663" t="s">
+      <c r="D665" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A668" t="s">
+    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A670" t="s">
         <v>292</v>
       </c>
-      <c r="B668" s="3" t="s">
+      <c r="B670" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C668" s="6">
+      <c r="C670" s="6">
         <v>5</v>
       </c>
-      <c r="D668" t="s">
+      <c r="D670" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A669" t="s">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A671" t="s">
         <v>292</v>
       </c>
-      <c r="B669" s="3" t="s">
+      <c r="B671" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C669" s="6">
+      <c r="C671" s="6">
         <v>5</v>
       </c>
-      <c r="D669" t="s">
+      <c r="D671" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A673" t="s">
-        <v>293</v>
-      </c>
-      <c r="B673" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C673" s="6">
-        <v>3.15</v>
-      </c>
-      <c r="D673" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A674" t="s">
-        <v>293</v>
-      </c>
-      <c r="B674" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C674" s="6">
-        <v>7.65</v>
-      </c>
-      <c r="D674" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.25">
@@ -10428,10 +10428,10 @@
         <v>293</v>
       </c>
       <c r="B675" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C675" s="6">
-        <v>8.1</v>
+        <v>3.15</v>
       </c>
       <c r="D675" t="s">
         <v>303</v>
@@ -10442,10 +10442,10 @@
         <v>293</v>
       </c>
       <c r="B676" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C676" s="6">
-        <v>10.8</v>
+        <v>7.65</v>
       </c>
       <c r="D676" t="s">
         <v>303</v>
@@ -10456,10 +10456,10 @@
         <v>293</v>
       </c>
       <c r="B677" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C677" s="6">
-        <v>12.2</v>
+        <v>8.1</v>
       </c>
       <c r="D677" t="s">
         <v>303</v>
@@ -10470,10 +10470,10 @@
         <v>293</v>
       </c>
       <c r="B678" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C678" s="6">
-        <v>11.25</v>
+        <v>10.8</v>
       </c>
       <c r="D678" t="s">
         <v>303</v>
@@ -10484,10 +10484,10 @@
         <v>293</v>
       </c>
       <c r="B679" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C679" s="6">
-        <v>11.25</v>
+        <v>12.2</v>
       </c>
       <c r="D679" t="s">
         <v>303</v>
@@ -10498,7 +10498,7 @@
         <v>293</v>
       </c>
       <c r="B680" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C680" s="6">
         <v>11.25</v>
@@ -10507,31 +10507,31 @@
         <v>303</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A683" t="s">
-        <v>294</v>
-      </c>
-      <c r="B683" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C683" s="6">
-        <v>3.36</v>
-      </c>
-      <c r="D683" t="s">
+    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A681" t="s">
+        <v>293</v>
+      </c>
+      <c r="B681" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C681" s="6">
+        <v>11.25</v>
+      </c>
+      <c r="D681" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A684" t="s">
-        <v>294</v>
-      </c>
-      <c r="B684" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C684" s="6">
-        <v>10.19</v>
-      </c>
-      <c r="D684" t="s">
+    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A682" t="s">
+        <v>293</v>
+      </c>
+      <c r="B682" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C682" s="6">
+        <v>11.25</v>
+      </c>
+      <c r="D682" t="s">
         <v>303</v>
       </c>
     </row>
@@ -10540,10 +10540,10 @@
         <v>294</v>
       </c>
       <c r="B685" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C685" s="6">
-        <v>14.4</v>
+        <v>3.36</v>
       </c>
       <c r="D685" t="s">
         <v>303</v>
@@ -10554,10 +10554,10 @@
         <v>294</v>
       </c>
       <c r="B686" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C686" s="6">
-        <v>14.39</v>
+        <v>10.19</v>
       </c>
       <c r="D686" t="s">
         <v>303</v>
@@ -10568,10 +10568,10 @@
         <v>294</v>
       </c>
       <c r="B687" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C687" s="6">
-        <v>11.52</v>
+        <v>14.4</v>
       </c>
       <c r="D687" t="s">
         <v>303</v>
@@ -10582,10 +10582,10 @@
         <v>294</v>
       </c>
       <c r="B688" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C688" s="6">
-        <v>12</v>
+        <v>14.39</v>
       </c>
       <c r="D688" t="s">
         <v>303</v>
@@ -10596,10 +10596,10 @@
         <v>294</v>
       </c>
       <c r="B689" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C689" s="6">
-        <v>12</v>
+        <v>11.52</v>
       </c>
       <c r="D689" t="s">
         <v>303</v>
@@ -10610,12 +10610,40 @@
         <v>294</v>
       </c>
       <c r="B690" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C690" s="6">
         <v>12</v>
       </c>
       <c r="D690" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="691" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A691" t="s">
+        <v>294</v>
+      </c>
+      <c r="B691" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C691" s="6">
+        <v>12</v>
+      </c>
+      <c r="D691" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="692" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A692" t="s">
+        <v>294</v>
+      </c>
+      <c r="B692" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C692" s="6">
+        <v>12</v>
+      </c>
+      <c r="D692" t="s">
         <v>303</v>
       </c>
     </row>

--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Garretts Reports\Sales Report App\Excell Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882D510E-3A6F-43A8-9910-B5C6E65588EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A84744-633E-4617-A9C0-581E505F04D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21150" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
+    <workbookView xWindow="43783" yWindow="-6386" windowWidth="33120" windowHeight="18275" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1895" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="339">
   <si>
     <t>BGC10</t>
   </si>
@@ -1439,7 +1439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6055176-08B8-4018-B9DF-7F26AB5DB49D}">
-  <dimension ref="A1:K692"/>
+  <dimension ref="A1:K693"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -9191,13 +9191,13 @@
         <v>276</v>
       </c>
       <c r="B572" s="3" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="C572" s="6">
-        <v>41.99</v>
+        <v>106.14</v>
       </c>
       <c r="D572" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.25">
@@ -9205,13 +9205,13 @@
         <v>276</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="C573" s="6">
-        <v>82</v>
+        <v>41.99</v>
       </c>
       <c r="D573" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.25">
@@ -9219,10 +9219,10 @@
         <v>276</v>
       </c>
       <c r="B574" s="3" t="s">
-        <v>256</v>
+        <v>58</v>
       </c>
       <c r="C574" s="6">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="D574" t="s">
         <v>145</v>
@@ -9233,13 +9233,13 @@
         <v>276</v>
       </c>
       <c r="B575" s="3" t="s">
-        <v>112</v>
+        <v>256</v>
       </c>
       <c r="C575" s="6">
-        <v>28.05</v>
+        <v>28</v>
       </c>
       <c r="D575" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.25">
@@ -9247,7 +9247,7 @@
         <v>276</v>
       </c>
       <c r="B576" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C576" s="6">
         <v>28.05</v>
@@ -9261,7 +9261,7 @@
         <v>276</v>
       </c>
       <c r="B577" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C577" s="6">
         <v>28.05</v>
@@ -9275,27 +9275,27 @@
         <v>276</v>
       </c>
       <c r="B578" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C578" s="6">
-        <v>11.2</v>
+        <v>28.05</v>
       </c>
       <c r="D578" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A581" t="s">
-        <v>144</v>
-      </c>
-      <c r="B581" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C581" s="6">
-        <v>29.87</v>
-      </c>
-      <c r="D581" t="s">
-        <v>136</v>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A579" t="s">
+        <v>276</v>
+      </c>
+      <c r="B579" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C579" s="6">
+        <v>11.2</v>
+      </c>
+      <c r="D579" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.25">
@@ -9303,13 +9303,13 @@
         <v>144</v>
       </c>
       <c r="B582" s="3" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C582" s="6">
-        <v>199</v>
+        <v>29.87</v>
       </c>
       <c r="D582" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.25">
@@ -9317,13 +9317,13 @@
         <v>144</v>
       </c>
       <c r="B583" s="3" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C583" s="6">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="D583" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.25">
@@ -9331,10 +9331,10 @@
         <v>144</v>
       </c>
       <c r="B584" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C584" s="6">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="D584" t="s">
         <v>142</v>
@@ -9345,10 +9345,10 @@
         <v>144</v>
       </c>
       <c r="B585" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C585" s="6">
-        <v>224.1</v>
+        <v>189</v>
       </c>
       <c r="D585" t="s">
         <v>142</v>
@@ -9359,10 +9359,10 @@
         <v>144</v>
       </c>
       <c r="B586" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C586" s="6">
-        <v>309</v>
+        <v>224.1</v>
       </c>
       <c r="D586" t="s">
         <v>142</v>
@@ -9372,25 +9372,25 @@
       <c r="A587" t="s">
         <v>144</v>
       </c>
-      <c r="B587" s="3">
-        <v>6102</v>
+      <c r="B587" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="C587" s="6">
-        <v>38.99</v>
+        <v>309</v>
       </c>
       <c r="D587" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>144</v>
       </c>
-      <c r="B588" s="3" t="s">
-        <v>212</v>
+      <c r="B588" s="3">
+        <v>6102</v>
       </c>
       <c r="C588" s="6">
-        <v>175</v>
+        <v>38.99</v>
       </c>
       <c r="D588" t="s">
         <v>144</v>
@@ -9401,10 +9401,10 @@
         <v>144</v>
       </c>
       <c r="B589" s="3" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C589" s="6">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="D589" t="s">
         <v>144</v>
@@ -9415,13 +9415,13 @@
         <v>144</v>
       </c>
       <c r="B590" s="3" t="s">
-        <v>57</v>
+        <v>202</v>
       </c>
       <c r="C590" s="6">
-        <v>59.99</v>
+        <v>134</v>
       </c>
       <c r="D590" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.25">
@@ -9429,10 +9429,10 @@
         <v>144</v>
       </c>
       <c r="B591" s="3" t="s">
-        <v>256</v>
+        <v>57</v>
       </c>
       <c r="C591" s="6">
-        <v>32.99</v>
+        <v>59.99</v>
       </c>
       <c r="D591" t="s">
         <v>145</v>
@@ -9443,10 +9443,10 @@
         <v>144</v>
       </c>
       <c r="B592" s="3" t="s">
-        <v>58</v>
+        <v>256</v>
       </c>
       <c r="C592" s="6">
-        <v>129</v>
+        <v>32.99</v>
       </c>
       <c r="D592" t="s">
         <v>145</v>
@@ -9457,10 +9457,10 @@
         <v>144</v>
       </c>
       <c r="B593" s="3" t="s">
-        <v>257</v>
+        <v>58</v>
       </c>
       <c r="C593" s="6">
-        <v>149.99</v>
+        <v>129</v>
       </c>
       <c r="D593" t="s">
         <v>145</v>
@@ -9471,13 +9471,13 @@
         <v>144</v>
       </c>
       <c r="B594" s="3" t="s">
-        <v>59</v>
+        <v>257</v>
       </c>
       <c r="C594" s="6">
-        <v>47.99</v>
+        <v>149.99</v>
       </c>
       <c r="D594" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.25">
@@ -9485,10 +9485,10 @@
         <v>144</v>
       </c>
       <c r="B595" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C595" s="6">
-        <v>39.99</v>
+        <v>47.99</v>
       </c>
       <c r="D595" t="s">
         <v>146</v>
@@ -9499,13 +9499,13 @@
         <v>144</v>
       </c>
       <c r="B596" s="3" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="C596" s="6">
         <v>39.99</v>
       </c>
       <c r="D596" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.25">
@@ -9513,7 +9513,10 @@
         <v>144</v>
       </c>
       <c r="B597" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
+      </c>
+      <c r="C597" s="6">
+        <v>39.99</v>
       </c>
       <c r="D597" t="s">
         <v>151</v>
@@ -9524,27 +9527,24 @@
         <v>144</v>
       </c>
       <c r="B598" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D598" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A599" t="s">
+        <v>144</v>
+      </c>
+      <c r="B599" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="C598" s="6">
+      <c r="C599" s="6">
         <v>36.950000000000003</v>
       </c>
-      <c r="D598" t="s">
+      <c r="D599" t="s">
         <v>173</v>
-      </c>
-    </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A601" t="s">
-        <v>288</v>
-      </c>
-      <c r="B601" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C601" s="6">
-        <v>18</v>
-      </c>
-      <c r="D601" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.25">
@@ -9552,10 +9552,10 @@
         <v>288</v>
       </c>
       <c r="B602" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C602" s="6">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="D602" t="s">
         <v>139</v>
@@ -9566,10 +9566,10 @@
         <v>288</v>
       </c>
       <c r="B603" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C603" s="6">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D603" t="s">
         <v>139</v>
@@ -9580,10 +9580,10 @@
         <v>288</v>
       </c>
       <c r="B604" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C604" s="6">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="D604" t="s">
         <v>139</v>
@@ -9594,10 +9594,10 @@
         <v>288</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C605" s="6">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="D605" t="s">
         <v>139</v>
@@ -9608,10 +9608,10 @@
         <v>288</v>
       </c>
       <c r="B606" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C606" s="6">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="D606" t="s">
         <v>139</v>
@@ -9622,10 +9622,10 @@
         <v>288</v>
       </c>
       <c r="B607" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C607" s="6">
-        <v>239</v>
+        <v>155</v>
       </c>
       <c r="D607" t="s">
         <v>139</v>
@@ -9636,10 +9636,10 @@
         <v>288</v>
       </c>
       <c r="B608" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C608" s="6">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="D608" t="s">
         <v>139</v>
@@ -9650,10 +9650,10 @@
         <v>288</v>
       </c>
       <c r="B609" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C609" s="6">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="D609" t="s">
         <v>139</v>
@@ -9664,10 +9664,10 @@
         <v>288</v>
       </c>
       <c r="B610" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C610" s="6">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="D610" t="s">
         <v>139</v>
@@ -9678,10 +9678,10 @@
         <v>288</v>
       </c>
       <c r="B611" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C611" s="6">
-        <v>285</v>
+        <v>210</v>
       </c>
       <c r="D611" t="s">
         <v>139</v>
@@ -9692,10 +9692,10 @@
         <v>288</v>
       </c>
       <c r="B612" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C612" s="6">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="D612" t="s">
         <v>139</v>
@@ -9706,13 +9706,13 @@
         <v>288</v>
       </c>
       <c r="B613" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C613" s="6">
-        <v>19.989999999999998</v>
+        <v>250</v>
       </c>
       <c r="D613" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.25">
@@ -9720,10 +9720,10 @@
         <v>288</v>
       </c>
       <c r="B614" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C614" s="6">
-        <v>29.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D614" t="s">
         <v>140</v>
@@ -9734,13 +9734,13 @@
         <v>288</v>
       </c>
       <c r="B615" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C615" s="6">
-        <v>155</v>
+        <v>29.99</v>
       </c>
       <c r="D615" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.25">
@@ -9748,10 +9748,10 @@
         <v>288</v>
       </c>
       <c r="B616" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C616" s="6">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="D616" t="s">
         <v>142</v>
@@ -9762,10 +9762,10 @@
         <v>288</v>
       </c>
       <c r="B617" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C617" s="6">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="D617" t="s">
         <v>142</v>
@@ -9776,10 +9776,10 @@
         <v>288</v>
       </c>
       <c r="B618" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C618" s="6">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D618" t="s">
         <v>142</v>
@@ -9790,10 +9790,10 @@
         <v>288</v>
       </c>
       <c r="B619" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C619" s="6">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="D619" t="s">
         <v>142</v>
@@ -9804,10 +9804,10 @@
         <v>288</v>
       </c>
       <c r="B620" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C620" s="6">
-        <v>260</v>
+        <v>199</v>
       </c>
       <c r="D620" t="s">
         <v>142</v>
@@ -9818,10 +9818,10 @@
         <v>288</v>
       </c>
       <c r="B621" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C621" s="6">
-        <v>389</v>
+        <v>260</v>
       </c>
       <c r="D621" t="s">
         <v>142</v>
@@ -9832,10 +9832,10 @@
         <v>288</v>
       </c>
       <c r="B622" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C622" s="6">
-        <v>399.99</v>
+        <v>389</v>
       </c>
       <c r="D622" t="s">
         <v>142</v>
@@ -9846,10 +9846,10 @@
         <v>288</v>
       </c>
       <c r="B623" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C623" s="6">
-        <v>89.23</v>
+        <v>399.99</v>
       </c>
       <c r="D623" t="s">
         <v>142</v>
@@ -9859,28 +9859,28 @@
       <c r="A624" t="s">
         <v>288</v>
       </c>
-      <c r="B624" s="3">
-        <v>6102</v>
+      <c r="B624" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="C624" s="6">
-        <v>44</v>
+        <v>89.23</v>
       </c>
       <c r="D624" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>288</v>
       </c>
-      <c r="B625" s="3" t="s">
-        <v>281</v>
+      <c r="B625" s="3">
+        <v>6102</v>
       </c>
       <c r="C625" s="6">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="D625" t="s">
-        <v>269</v>
+        <v>144</v>
       </c>
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.25">
@@ -9888,10 +9888,10 @@
         <v>288</v>
       </c>
       <c r="B626" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C626" s="6">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D626" t="s">
         <v>269</v>
@@ -9902,10 +9902,10 @@
         <v>288</v>
       </c>
       <c r="B627" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C627" s="6">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D627" t="s">
         <v>269</v>
@@ -9916,10 +9916,10 @@
         <v>288</v>
       </c>
       <c r="B628" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C628" s="6">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D628" t="s">
         <v>269</v>
@@ -9930,10 +9930,10 @@
         <v>288</v>
       </c>
       <c r="B629" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C629" s="6">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D629" t="s">
         <v>269</v>
@@ -9944,10 +9944,10 @@
         <v>288</v>
       </c>
       <c r="B630" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C630" s="6">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="D630" t="s">
         <v>269</v>
@@ -9958,13 +9958,13 @@
         <v>288</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>55</v>
+        <v>286</v>
       </c>
       <c r="C631" s="6">
-        <v>27.99</v>
+        <v>114</v>
       </c>
       <c r="D631" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.25">
@@ -9972,10 +9972,10 @@
         <v>288</v>
       </c>
       <c r="B632" s="3" t="s">
-        <v>255</v>
+        <v>55</v>
       </c>
       <c r="C632" s="6">
-        <v>28.99</v>
+        <v>27.99</v>
       </c>
       <c r="D632" t="s">
         <v>145</v>
@@ -9986,10 +9986,10 @@
         <v>288</v>
       </c>
       <c r="B633" s="3" t="s">
-        <v>56</v>
+        <v>255</v>
       </c>
       <c r="C633" s="6">
-        <v>39.99</v>
+        <v>28.99</v>
       </c>
       <c r="D633" t="s">
         <v>145</v>
@@ -10000,10 +10000,10 @@
         <v>288</v>
       </c>
       <c r="B634" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C634" s="6">
-        <v>58</v>
+        <v>39.99</v>
       </c>
       <c r="D634" t="s">
         <v>145</v>
@@ -10014,10 +10014,10 @@
         <v>288</v>
       </c>
       <c r="B635" s="3" t="s">
-        <v>256</v>
+        <v>57</v>
       </c>
       <c r="C635" s="6">
-        <v>42.99</v>
+        <v>58</v>
       </c>
       <c r="D635" t="s">
         <v>145</v>
@@ -10028,10 +10028,10 @@
         <v>288</v>
       </c>
       <c r="B636" s="3" t="s">
-        <v>58</v>
+        <v>256</v>
       </c>
       <c r="C636" s="6">
-        <v>129</v>
+        <v>42.99</v>
       </c>
       <c r="D636" t="s">
         <v>145</v>
@@ -10042,10 +10042,10 @@
         <v>288</v>
       </c>
       <c r="B637" s="3" t="s">
-        <v>257</v>
+        <v>58</v>
       </c>
       <c r="C637" s="6">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="D637" t="s">
         <v>145</v>
@@ -10056,13 +10056,13 @@
         <v>288</v>
       </c>
       <c r="B638" s="3" t="s">
-        <v>59</v>
+        <v>257</v>
       </c>
       <c r="C638" s="6">
-        <v>54.5</v>
+        <v>180</v>
       </c>
       <c r="D638" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.25">
@@ -10070,10 +10070,10 @@
         <v>288</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C639" s="6">
-        <v>48.99</v>
+        <v>54.5</v>
       </c>
       <c r="D639" t="s">
         <v>146</v>
@@ -10084,10 +10084,10 @@
         <v>288</v>
       </c>
       <c r="B640" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C640" s="6">
-        <v>39.99</v>
+        <v>48.99</v>
       </c>
       <c r="D640" t="s">
         <v>146</v>
@@ -10098,10 +10098,10 @@
         <v>288</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C641" s="6">
-        <v>64.989999999999995</v>
+        <v>39.99</v>
       </c>
       <c r="D641" t="s">
         <v>146</v>
@@ -10112,10 +10112,10 @@
         <v>288</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C642" s="6">
-        <v>29.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="D642" t="s">
         <v>146</v>
@@ -10126,10 +10126,10 @@
         <v>288</v>
       </c>
       <c r="B643" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C643" s="6">
-        <v>28.99</v>
+        <v>29.99</v>
       </c>
       <c r="D643" t="s">
         <v>146</v>
@@ -10140,7 +10140,10 @@
         <v>288</v>
       </c>
       <c r="B644" s="3" t="s">
-        <v>176</v>
+        <v>66</v>
+      </c>
+      <c r="C644" s="6">
+        <v>28.99</v>
       </c>
       <c r="D644" t="s">
         <v>146</v>
@@ -10151,10 +10154,7 @@
         <v>288</v>
       </c>
       <c r="B645" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C645" s="6">
-        <v>29.99</v>
+        <v>176</v>
       </c>
       <c r="D645" t="s">
         <v>146</v>
@@ -10165,10 +10165,10 @@
         <v>288</v>
       </c>
       <c r="B646" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C646" s="6">
-        <v>25.99</v>
+        <v>29.99</v>
       </c>
       <c r="D646" t="s">
         <v>146</v>
@@ -10178,28 +10178,28 @@
       <c r="A647" t="s">
         <v>288</v>
       </c>
-      <c r="B647" s="3">
-        <v>6642</v>
+      <c r="B647" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="C647" s="6">
-        <v>50</v>
+        <v>25.99</v>
       </c>
       <c r="D647" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>288</v>
       </c>
-      <c r="B648" s="3" t="s">
-        <v>117</v>
+      <c r="B648" s="3">
+        <v>6642</v>
       </c>
       <c r="C648" s="6">
-        <v>19.2</v>
+        <v>50</v>
       </c>
       <c r="D648" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.25">
@@ -10207,10 +10207,10 @@
         <v>288</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C649" s="6">
-        <v>40</v>
+        <v>19.2</v>
       </c>
       <c r="D649" t="s">
         <v>152</v>
@@ -10221,7 +10221,7 @@
         <v>288</v>
       </c>
       <c r="B650" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C650" s="6">
         <v>40</v>
@@ -10235,13 +10235,13 @@
         <v>288</v>
       </c>
       <c r="B651" s="3" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="C651" s="6">
-        <v>30.58</v>
+        <v>40</v>
       </c>
       <c r="D651" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.25">
@@ -10249,10 +10249,10 @@
         <v>288</v>
       </c>
       <c r="B652" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C652" s="6">
-        <v>39.99</v>
+        <v>30.58</v>
       </c>
       <c r="D652" t="s">
         <v>154</v>
@@ -10263,27 +10263,27 @@
         <v>288</v>
       </c>
       <c r="B653" s="3" t="s">
-        <v>287</v>
+        <v>127</v>
       </c>
       <c r="C653" s="6">
-        <v>90</v>
+        <v>39.99</v>
       </c>
       <c r="D653" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A656" t="s">
-        <v>290</v>
-      </c>
-      <c r="B656" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C656" s="6">
-        <v>42.75</v>
-      </c>
-      <c r="D656" t="s">
-        <v>139</v>
+    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A654" t="s">
+        <v>288</v>
+      </c>
+      <c r="B654" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C654" s="6">
+        <v>90</v>
+      </c>
+      <c r="D654" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.25">
@@ -10291,10 +10291,10 @@
         <v>290</v>
       </c>
       <c r="B657" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C657" s="6">
-        <v>68</v>
+        <v>42.75</v>
       </c>
       <c r="D657" t="s">
         <v>139</v>
@@ -10305,27 +10305,27 @@
         <v>290</v>
       </c>
       <c r="B658" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C658" s="6">
-        <v>82.2</v>
+        <v>68</v>
       </c>
       <c r="D658" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A660" t="s">
-        <v>304</v>
-      </c>
-      <c r="B660" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C660" s="6">
-        <v>10</v>
-      </c>
-      <c r="D660" t="s">
-        <v>140</v>
+    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A659" t="s">
+        <v>290</v>
+      </c>
+      <c r="B659" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C659" s="6">
+        <v>82.2</v>
+      </c>
+      <c r="D659" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.25">
@@ -10333,7 +10333,10 @@
         <v>304</v>
       </c>
       <c r="B661" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="C661" s="6">
+        <v>10</v>
       </c>
       <c r="D661" t="s">
         <v>140</v>
@@ -10343,14 +10346,11 @@
       <c r="A662" t="s">
         <v>304</v>
       </c>
-      <c r="B662" s="3">
-        <v>4642</v>
-      </c>
-      <c r="C662" s="6">
-        <v>18.96</v>
+      <c r="B662" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D662" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.25">
@@ -10358,10 +10358,10 @@
         <v>304</v>
       </c>
       <c r="B663" s="3">
-        <v>6642</v>
+        <v>4642</v>
       </c>
       <c r="C663" s="6">
-        <v>22.37</v>
+        <v>18.96</v>
       </c>
       <c r="D663" t="s">
         <v>148</v>
@@ -10371,14 +10371,14 @@
       <c r="A664" t="s">
         <v>304</v>
       </c>
-      <c r="B664" s="3" t="s">
-        <v>116</v>
+      <c r="B664" s="3">
+        <v>6642</v>
       </c>
       <c r="C664" s="6">
-        <v>9.1</v>
+        <v>22.37</v>
       </c>
       <c r="D664" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.25">
@@ -10386,7 +10386,7 @@
         <v>304</v>
       </c>
       <c r="B665" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C665" s="6">
         <v>9.1</v>
@@ -10395,18 +10395,18 @@
         <v>152</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A670" t="s">
-        <v>292</v>
-      </c>
-      <c r="B670" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C670" s="6">
-        <v>5</v>
-      </c>
-      <c r="D670" t="s">
-        <v>140</v>
+    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A666" t="s">
+        <v>304</v>
+      </c>
+      <c r="B666" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C666" s="6">
+        <v>9.1</v>
+      </c>
+      <c r="D666" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.25">
@@ -10414,7 +10414,7 @@
         <v>292</v>
       </c>
       <c r="B671" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C671" s="6">
         <v>5</v>
@@ -10423,18 +10423,18 @@
         <v>140</v>
       </c>
     </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A675" t="s">
-        <v>293</v>
-      </c>
-      <c r="B675" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C675" s="6">
-        <v>3.15</v>
-      </c>
-      <c r="D675" t="s">
-        <v>303</v>
+    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A672" t="s">
+        <v>292</v>
+      </c>
+      <c r="B672" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C672" s="6">
+        <v>5</v>
+      </c>
+      <c r="D672" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.25">
@@ -10442,10 +10442,10 @@
         <v>293</v>
       </c>
       <c r="B676" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C676" s="6">
-        <v>7.65</v>
+        <v>3.15</v>
       </c>
       <c r="D676" t="s">
         <v>303</v>
@@ -10456,10 +10456,10 @@
         <v>293</v>
       </c>
       <c r="B677" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C677" s="6">
-        <v>8.1</v>
+        <v>7.65</v>
       </c>
       <c r="D677" t="s">
         <v>303</v>
@@ -10470,10 +10470,10 @@
         <v>293</v>
       </c>
       <c r="B678" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C678" s="6">
-        <v>10.8</v>
+        <v>8.1</v>
       </c>
       <c r="D678" t="s">
         <v>303</v>
@@ -10484,10 +10484,10 @@
         <v>293</v>
       </c>
       <c r="B679" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C679" s="6">
-        <v>12.2</v>
+        <v>10.8</v>
       </c>
       <c r="D679" t="s">
         <v>303</v>
@@ -10498,10 +10498,10 @@
         <v>293</v>
       </c>
       <c r="B680" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C680" s="6">
-        <v>11.25</v>
+        <v>12.2</v>
       </c>
       <c r="D680" t="s">
         <v>303</v>
@@ -10512,7 +10512,7 @@
         <v>293</v>
       </c>
       <c r="B681" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C681" s="6">
         <v>11.25</v>
@@ -10526,7 +10526,7 @@
         <v>293</v>
       </c>
       <c r="B682" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C682" s="6">
         <v>11.25</v>
@@ -10535,17 +10535,17 @@
         <v>303</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A685" t="s">
-        <v>294</v>
-      </c>
-      <c r="B685" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C685" s="6">
-        <v>3.36</v>
-      </c>
-      <c r="D685" t="s">
+    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A683" t="s">
+        <v>293</v>
+      </c>
+      <c r="B683" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C683" s="6">
+        <v>11.25</v>
+      </c>
+      <c r="D683" t="s">
         <v>303</v>
       </c>
     </row>
@@ -10554,10 +10554,10 @@
         <v>294</v>
       </c>
       <c r="B686" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C686" s="6">
-        <v>10.19</v>
+        <v>3.36</v>
       </c>
       <c r="D686" t="s">
         <v>303</v>
@@ -10568,10 +10568,10 @@
         <v>294</v>
       </c>
       <c r="B687" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C687" s="6">
-        <v>14.4</v>
+        <v>10.19</v>
       </c>
       <c r="D687" t="s">
         <v>303</v>
@@ -10582,10 +10582,10 @@
         <v>294</v>
       </c>
       <c r="B688" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C688" s="6">
-        <v>14.39</v>
+        <v>14.4</v>
       </c>
       <c r="D688" t="s">
         <v>303</v>
@@ -10596,10 +10596,10 @@
         <v>294</v>
       </c>
       <c r="B689" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C689" s="6">
-        <v>11.52</v>
+        <v>14.39</v>
       </c>
       <c r="D689" t="s">
         <v>303</v>
@@ -10610,10 +10610,10 @@
         <v>294</v>
       </c>
       <c r="B690" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C690" s="6">
-        <v>12</v>
+        <v>11.52</v>
       </c>
       <c r="D690" t="s">
         <v>303</v>
@@ -10624,7 +10624,7 @@
         <v>294</v>
       </c>
       <c r="B691" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C691" s="6">
         <v>12</v>
@@ -10638,12 +10638,26 @@
         <v>294</v>
       </c>
       <c r="B692" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C692" s="6">
         <v>12</v>
       </c>
       <c r="D692" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="693" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A693" t="s">
+        <v>294</v>
+      </c>
+      <c r="B693" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C693" s="6">
+        <v>12</v>
+      </c>
+      <c r="D693" t="s">
         <v>303</v>
       </c>
     </row>

--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Garretts Reports\Sales Report App\Excell Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A84744-633E-4617-A9C0-581E505F04D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3789B771-1965-4680-B679-5831B77082B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43783" yWindow="-6386" windowWidth="33120" windowHeight="18275" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
+    <workbookView xWindow="3510" yWindow="1905" windowWidth="12120" windowHeight="19695" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1901" uniqueCount="339">
   <si>
     <t>BGC10</t>
   </si>
@@ -1439,7 +1439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6055176-08B8-4018-B9DF-7F26AB5DB49D}">
-  <dimension ref="A1:K693"/>
+  <dimension ref="A1:K694"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -9386,25 +9386,25 @@
       <c r="A588" t="s">
         <v>144</v>
       </c>
-      <c r="B588" s="3">
-        <v>6102</v>
+      <c r="B588" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="C588" s="6">
-        <v>38.99</v>
+        <v>85.5</v>
       </c>
       <c r="D588" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>144</v>
       </c>
-      <c r="B589" s="3" t="s">
-        <v>212</v>
+      <c r="B589" s="3">
+        <v>6102</v>
       </c>
       <c r="C589" s="6">
-        <v>175</v>
+        <v>38.99</v>
       </c>
       <c r="D589" t="s">
         <v>144</v>
@@ -9415,10 +9415,10 @@
         <v>144</v>
       </c>
       <c r="B590" s="3" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C590" s="6">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="D590" t="s">
         <v>144</v>
@@ -9429,13 +9429,13 @@
         <v>144</v>
       </c>
       <c r="B591" s="3" t="s">
-        <v>57</v>
+        <v>202</v>
       </c>
       <c r="C591" s="6">
-        <v>59.99</v>
+        <v>134</v>
       </c>
       <c r="D591" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.25">
@@ -9443,10 +9443,10 @@
         <v>144</v>
       </c>
       <c r="B592" s="3" t="s">
-        <v>256</v>
+        <v>57</v>
       </c>
       <c r="C592" s="6">
-        <v>32.99</v>
+        <v>59.99</v>
       </c>
       <c r="D592" t="s">
         <v>145</v>
@@ -9457,10 +9457,10 @@
         <v>144</v>
       </c>
       <c r="B593" s="3" t="s">
-        <v>58</v>
+        <v>256</v>
       </c>
       <c r="C593" s="6">
-        <v>129</v>
+        <v>32.99</v>
       </c>
       <c r="D593" t="s">
         <v>145</v>
@@ -9471,10 +9471,10 @@
         <v>144</v>
       </c>
       <c r="B594" s="3" t="s">
-        <v>257</v>
+        <v>58</v>
       </c>
       <c r="C594" s="6">
-        <v>149.99</v>
+        <v>129</v>
       </c>
       <c r="D594" t="s">
         <v>145</v>
@@ -9485,13 +9485,13 @@
         <v>144</v>
       </c>
       <c r="B595" s="3" t="s">
-        <v>59</v>
+        <v>257</v>
       </c>
       <c r="C595" s="6">
-        <v>47.99</v>
+        <v>149.99</v>
       </c>
       <c r="D595" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.25">
@@ -9499,10 +9499,10 @@
         <v>144</v>
       </c>
       <c r="B596" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C596" s="6">
-        <v>39.99</v>
+        <v>47.99</v>
       </c>
       <c r="D596" t="s">
         <v>146</v>
@@ -9513,13 +9513,13 @@
         <v>144</v>
       </c>
       <c r="B597" s="3" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="C597" s="6">
         <v>39.99</v>
       </c>
       <c r="D597" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.25">
@@ -9527,7 +9527,10 @@
         <v>144</v>
       </c>
       <c r="B598" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
+      </c>
+      <c r="C598" s="6">
+        <v>39.99</v>
       </c>
       <c r="D598" t="s">
         <v>151</v>
@@ -9538,27 +9541,24 @@
         <v>144</v>
       </c>
       <c r="B599" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D599" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A600" t="s">
+        <v>144</v>
+      </c>
+      <c r="B600" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="C599" s="6">
+      <c r="C600" s="6">
         <v>36.950000000000003</v>
       </c>
-      <c r="D599" t="s">
+      <c r="D600" t="s">
         <v>173</v>
-      </c>
-    </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A602" t="s">
-        <v>288</v>
-      </c>
-      <c r="B602" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C602" s="6">
-        <v>18</v>
-      </c>
-      <c r="D602" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.25">
@@ -9566,10 +9566,10 @@
         <v>288</v>
       </c>
       <c r="B603" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C603" s="6">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="D603" t="s">
         <v>139</v>
@@ -9580,10 +9580,10 @@
         <v>288</v>
       </c>
       <c r="B604" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C604" s="6">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D604" t="s">
         <v>139</v>
@@ -9594,10 +9594,10 @@
         <v>288</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C605" s="6">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="D605" t="s">
         <v>139</v>
@@ -9608,10 +9608,10 @@
         <v>288</v>
       </c>
       <c r="B606" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C606" s="6">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="D606" t="s">
         <v>139</v>
@@ -9622,10 +9622,10 @@
         <v>288</v>
       </c>
       <c r="B607" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C607" s="6">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="D607" t="s">
         <v>139</v>
@@ -9636,10 +9636,10 @@
         <v>288</v>
       </c>
       <c r="B608" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C608" s="6">
-        <v>239</v>
+        <v>155</v>
       </c>
       <c r="D608" t="s">
         <v>139</v>
@@ -9650,10 +9650,10 @@
         <v>288</v>
       </c>
       <c r="B609" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C609" s="6">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="D609" t="s">
         <v>139</v>
@@ -9664,10 +9664,10 @@
         <v>288</v>
       </c>
       <c r="B610" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C610" s="6">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="D610" t="s">
         <v>139</v>
@@ -9678,10 +9678,10 @@
         <v>288</v>
       </c>
       <c r="B611" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C611" s="6">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="D611" t="s">
         <v>139</v>
@@ -9692,10 +9692,10 @@
         <v>288</v>
       </c>
       <c r="B612" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C612" s="6">
-        <v>285</v>
+        <v>210</v>
       </c>
       <c r="D612" t="s">
         <v>139</v>
@@ -9706,10 +9706,10 @@
         <v>288</v>
       </c>
       <c r="B613" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C613" s="6">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="D613" t="s">
         <v>139</v>
@@ -9720,13 +9720,13 @@
         <v>288</v>
       </c>
       <c r="B614" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C614" s="6">
-        <v>19.989999999999998</v>
+        <v>250</v>
       </c>
       <c r="D614" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.25">
@@ -9734,10 +9734,10 @@
         <v>288</v>
       </c>
       <c r="B615" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C615" s="6">
-        <v>29.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D615" t="s">
         <v>140</v>
@@ -9748,13 +9748,13 @@
         <v>288</v>
       </c>
       <c r="B616" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C616" s="6">
-        <v>155</v>
+        <v>29.99</v>
       </c>
       <c r="D616" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.25">
@@ -9762,10 +9762,10 @@
         <v>288</v>
       </c>
       <c r="B617" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C617" s="6">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="D617" t="s">
         <v>142</v>
@@ -9776,10 +9776,10 @@
         <v>288</v>
       </c>
       <c r="B618" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C618" s="6">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="D618" t="s">
         <v>142</v>
@@ -9790,10 +9790,10 @@
         <v>288</v>
       </c>
       <c r="B619" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C619" s="6">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D619" t="s">
         <v>142</v>
@@ -9804,10 +9804,10 @@
         <v>288</v>
       </c>
       <c r="B620" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C620" s="6">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="D620" t="s">
         <v>142</v>
@@ -9818,10 +9818,10 @@
         <v>288</v>
       </c>
       <c r="B621" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C621" s="6">
-        <v>260</v>
+        <v>199</v>
       </c>
       <c r="D621" t="s">
         <v>142</v>
@@ -9832,10 +9832,10 @@
         <v>288</v>
       </c>
       <c r="B622" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C622" s="6">
-        <v>389</v>
+        <v>260</v>
       </c>
       <c r="D622" t="s">
         <v>142</v>
@@ -9846,10 +9846,10 @@
         <v>288</v>
       </c>
       <c r="B623" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C623" s="6">
-        <v>399.99</v>
+        <v>389</v>
       </c>
       <c r="D623" t="s">
         <v>142</v>
@@ -9860,10 +9860,10 @@
         <v>288</v>
       </c>
       <c r="B624" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C624" s="6">
-        <v>89.23</v>
+        <v>399.99</v>
       </c>
       <c r="D624" t="s">
         <v>142</v>
@@ -9873,28 +9873,28 @@
       <c r="A625" t="s">
         <v>288</v>
       </c>
-      <c r="B625" s="3">
-        <v>6102</v>
+      <c r="B625" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="C625" s="6">
-        <v>44</v>
+        <v>89.23</v>
       </c>
       <c r="D625" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>288</v>
       </c>
-      <c r="B626" s="3" t="s">
-        <v>281</v>
+      <c r="B626" s="3">
+        <v>6102</v>
       </c>
       <c r="C626" s="6">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="D626" t="s">
-        <v>269</v>
+        <v>144</v>
       </c>
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.25">
@@ -9902,10 +9902,10 @@
         <v>288</v>
       </c>
       <c r="B627" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C627" s="6">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D627" t="s">
         <v>269</v>
@@ -9916,10 +9916,10 @@
         <v>288</v>
       </c>
       <c r="B628" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C628" s="6">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D628" t="s">
         <v>269</v>
@@ -9930,10 +9930,10 @@
         <v>288</v>
       </c>
       <c r="B629" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C629" s="6">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D629" t="s">
         <v>269</v>
@@ -9944,10 +9944,10 @@
         <v>288</v>
       </c>
       <c r="B630" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C630" s="6">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D630" t="s">
         <v>269</v>
@@ -9958,10 +9958,10 @@
         <v>288</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C631" s="6">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="D631" t="s">
         <v>269</v>
@@ -9972,13 +9972,13 @@
         <v>288</v>
       </c>
       <c r="B632" s="3" t="s">
-        <v>55</v>
+        <v>286</v>
       </c>
       <c r="C632" s="6">
-        <v>27.99</v>
+        <v>114</v>
       </c>
       <c r="D632" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.25">
@@ -9986,10 +9986,10 @@
         <v>288</v>
       </c>
       <c r="B633" s="3" t="s">
-        <v>255</v>
+        <v>55</v>
       </c>
       <c r="C633" s="6">
-        <v>28.99</v>
+        <v>27.99</v>
       </c>
       <c r="D633" t="s">
         <v>145</v>
@@ -10000,10 +10000,10 @@
         <v>288</v>
       </c>
       <c r="B634" s="3" t="s">
-        <v>56</v>
+        <v>255</v>
       </c>
       <c r="C634" s="6">
-        <v>39.99</v>
+        <v>28.99</v>
       </c>
       <c r="D634" t="s">
         <v>145</v>
@@ -10014,10 +10014,10 @@
         <v>288</v>
       </c>
       <c r="B635" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C635" s="6">
-        <v>58</v>
+        <v>39.99</v>
       </c>
       <c r="D635" t="s">
         <v>145</v>
@@ -10028,10 +10028,10 @@
         <v>288</v>
       </c>
       <c r="B636" s="3" t="s">
-        <v>256</v>
+        <v>57</v>
       </c>
       <c r="C636" s="6">
-        <v>42.99</v>
+        <v>58</v>
       </c>
       <c r="D636" t="s">
         <v>145</v>
@@ -10042,10 +10042,10 @@
         <v>288</v>
       </c>
       <c r="B637" s="3" t="s">
-        <v>58</v>
+        <v>256</v>
       </c>
       <c r="C637" s="6">
-        <v>129</v>
+        <v>42.99</v>
       </c>
       <c r="D637" t="s">
         <v>145</v>
@@ -10056,10 +10056,10 @@
         <v>288</v>
       </c>
       <c r="B638" s="3" t="s">
-        <v>257</v>
+        <v>58</v>
       </c>
       <c r="C638" s="6">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="D638" t="s">
         <v>145</v>
@@ -10070,13 +10070,13 @@
         <v>288</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>59</v>
+        <v>257</v>
       </c>
       <c r="C639" s="6">
-        <v>54.5</v>
+        <v>180</v>
       </c>
       <c r="D639" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.25">
@@ -10084,10 +10084,10 @@
         <v>288</v>
       </c>
       <c r="B640" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C640" s="6">
-        <v>48.99</v>
+        <v>54.5</v>
       </c>
       <c r="D640" t="s">
         <v>146</v>
@@ -10098,10 +10098,10 @@
         <v>288</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C641" s="6">
-        <v>39.99</v>
+        <v>48.99</v>
       </c>
       <c r="D641" t="s">
         <v>146</v>
@@ -10112,10 +10112,10 @@
         <v>288</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C642" s="6">
-        <v>64.989999999999995</v>
+        <v>39.99</v>
       </c>
       <c r="D642" t="s">
         <v>146</v>
@@ -10126,10 +10126,10 @@
         <v>288</v>
       </c>
       <c r="B643" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C643" s="6">
-        <v>29.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="D643" t="s">
         <v>146</v>
@@ -10140,10 +10140,10 @@
         <v>288</v>
       </c>
       <c r="B644" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C644" s="6">
-        <v>28.99</v>
+        <v>29.99</v>
       </c>
       <c r="D644" t="s">
         <v>146</v>
@@ -10154,7 +10154,10 @@
         <v>288</v>
       </c>
       <c r="B645" s="3" t="s">
-        <v>176</v>
+        <v>66</v>
+      </c>
+      <c r="C645" s="6">
+        <v>28.99</v>
       </c>
       <c r="D645" t="s">
         <v>146</v>
@@ -10165,10 +10168,7 @@
         <v>288</v>
       </c>
       <c r="B646" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C646" s="6">
-        <v>29.99</v>
+        <v>176</v>
       </c>
       <c r="D646" t="s">
         <v>146</v>
@@ -10179,10 +10179,10 @@
         <v>288</v>
       </c>
       <c r="B647" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C647" s="6">
-        <v>25.99</v>
+        <v>29.99</v>
       </c>
       <c r="D647" t="s">
         <v>146</v>
@@ -10192,28 +10192,28 @@
       <c r="A648" t="s">
         <v>288</v>
       </c>
-      <c r="B648" s="3">
-        <v>6642</v>
+      <c r="B648" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="C648" s="6">
-        <v>50</v>
+        <v>25.99</v>
       </c>
       <c r="D648" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>288</v>
       </c>
-      <c r="B649" s="3" t="s">
-        <v>117</v>
+      <c r="B649" s="3">
+        <v>6642</v>
       </c>
       <c r="C649" s="6">
-        <v>19.2</v>
+        <v>50</v>
       </c>
       <c r="D649" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.25">
@@ -10221,10 +10221,10 @@
         <v>288</v>
       </c>
       <c r="B650" s="3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C650" s="6">
-        <v>40</v>
+        <v>19.2</v>
       </c>
       <c r="D650" t="s">
         <v>152</v>
@@ -10235,7 +10235,7 @@
         <v>288</v>
       </c>
       <c r="B651" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C651" s="6">
         <v>40</v>
@@ -10249,13 +10249,13 @@
         <v>288</v>
       </c>
       <c r="B652" s="3" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="C652" s="6">
-        <v>30.58</v>
+        <v>40</v>
       </c>
       <c r="D652" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.25">
@@ -10263,10 +10263,10 @@
         <v>288</v>
       </c>
       <c r="B653" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C653" s="6">
-        <v>39.99</v>
+        <v>30.58</v>
       </c>
       <c r="D653" t="s">
         <v>154</v>
@@ -10277,27 +10277,27 @@
         <v>288</v>
       </c>
       <c r="B654" s="3" t="s">
-        <v>287</v>
+        <v>127</v>
       </c>
       <c r="C654" s="6">
-        <v>90</v>
+        <v>39.99</v>
       </c>
       <c r="D654" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A657" t="s">
-        <v>290</v>
-      </c>
-      <c r="B657" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C657" s="6">
-        <v>42.75</v>
-      </c>
-      <c r="D657" t="s">
-        <v>139</v>
+    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A655" t="s">
+        <v>288</v>
+      </c>
+      <c r="B655" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C655" s="6">
+        <v>90</v>
+      </c>
+      <c r="D655" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.25">
@@ -10305,10 +10305,10 @@
         <v>290</v>
       </c>
       <c r="B658" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C658" s="6">
-        <v>68</v>
+        <v>42.75</v>
       </c>
       <c r="D658" t="s">
         <v>139</v>
@@ -10319,27 +10319,27 @@
         <v>290</v>
       </c>
       <c r="B659" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C659" s="6">
-        <v>82.2</v>
+        <v>68</v>
       </c>
       <c r="D659" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A661" t="s">
-        <v>304</v>
-      </c>
-      <c r="B661" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C661" s="6">
-        <v>10</v>
-      </c>
-      <c r="D661" t="s">
-        <v>140</v>
+    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A660" t="s">
+        <v>290</v>
+      </c>
+      <c r="B660" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C660" s="6">
+        <v>82.2</v>
+      </c>
+      <c r="D660" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.25">
@@ -10347,7 +10347,10 @@
         <v>304</v>
       </c>
       <c r="B662" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="C662" s="6">
+        <v>10</v>
       </c>
       <c r="D662" t="s">
         <v>140</v>
@@ -10357,14 +10360,11 @@
       <c r="A663" t="s">
         <v>304</v>
       </c>
-      <c r="B663" s="3">
-        <v>4642</v>
-      </c>
-      <c r="C663" s="6">
-        <v>18.96</v>
+      <c r="B663" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D663" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.25">
@@ -10372,10 +10372,10 @@
         <v>304</v>
       </c>
       <c r="B664" s="3">
-        <v>6642</v>
+        <v>4642</v>
       </c>
       <c r="C664" s="6">
-        <v>22.37</v>
+        <v>18.96</v>
       </c>
       <c r="D664" t="s">
         <v>148</v>
@@ -10385,14 +10385,14 @@
       <c r="A665" t="s">
         <v>304</v>
       </c>
-      <c r="B665" s="3" t="s">
-        <v>116</v>
+      <c r="B665" s="3">
+        <v>6642</v>
       </c>
       <c r="C665" s="6">
-        <v>9.1</v>
+        <v>22.37</v>
       </c>
       <c r="D665" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.25">
@@ -10400,7 +10400,7 @@
         <v>304</v>
       </c>
       <c r="B666" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C666" s="6">
         <v>9.1</v>
@@ -10409,18 +10409,18 @@
         <v>152</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A671" t="s">
-        <v>292</v>
-      </c>
-      <c r="B671" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C671" s="6">
-        <v>5</v>
-      </c>
-      <c r="D671" t="s">
-        <v>140</v>
+    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A667" t="s">
+        <v>304</v>
+      </c>
+      <c r="B667" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C667" s="6">
+        <v>9.1</v>
+      </c>
+      <c r="D667" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.25">
@@ -10428,7 +10428,7 @@
         <v>292</v>
       </c>
       <c r="B672" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C672" s="6">
         <v>5</v>
@@ -10437,18 +10437,18 @@
         <v>140</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A676" t="s">
-        <v>293</v>
-      </c>
-      <c r="B676" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C676" s="6">
-        <v>3.15</v>
-      </c>
-      <c r="D676" t="s">
-        <v>303</v>
+    <row r="673" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A673" t="s">
+        <v>292</v>
+      </c>
+      <c r="B673" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C673" s="6">
+        <v>5</v>
+      </c>
+      <c r="D673" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.25">
@@ -10456,10 +10456,10 @@
         <v>293</v>
       </c>
       <c r="B677" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C677" s="6">
-        <v>7.65</v>
+        <v>3.15</v>
       </c>
       <c r="D677" t="s">
         <v>303</v>
@@ -10470,10 +10470,10 @@
         <v>293</v>
       </c>
       <c r="B678" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C678" s="6">
-        <v>8.1</v>
+        <v>7.65</v>
       </c>
       <c r="D678" t="s">
         <v>303</v>
@@ -10484,10 +10484,10 @@
         <v>293</v>
       </c>
       <c r="B679" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C679" s="6">
-        <v>10.8</v>
+        <v>8.1</v>
       </c>
       <c r="D679" t="s">
         <v>303</v>
@@ -10498,10 +10498,10 @@
         <v>293</v>
       </c>
       <c r="B680" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C680" s="6">
-        <v>12.2</v>
+        <v>10.8</v>
       </c>
       <c r="D680" t="s">
         <v>303</v>
@@ -10512,10 +10512,10 @@
         <v>293</v>
       </c>
       <c r="B681" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C681" s="6">
-        <v>11.25</v>
+        <v>12.2</v>
       </c>
       <c r="D681" t="s">
         <v>303</v>
@@ -10526,7 +10526,7 @@
         <v>293</v>
       </c>
       <c r="B682" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C682" s="6">
         <v>11.25</v>
@@ -10540,7 +10540,7 @@
         <v>293</v>
       </c>
       <c r="B683" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C683" s="6">
         <v>11.25</v>
@@ -10549,17 +10549,17 @@
         <v>303</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A686" t="s">
-        <v>294</v>
-      </c>
-      <c r="B686" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C686" s="6">
-        <v>3.36</v>
-      </c>
-      <c r="D686" t="s">
+    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A684" t="s">
+        <v>293</v>
+      </c>
+      <c r="B684" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C684" s="6">
+        <v>11.25</v>
+      </c>
+      <c r="D684" t="s">
         <v>303</v>
       </c>
     </row>
@@ -10568,10 +10568,10 @@
         <v>294</v>
       </c>
       <c r="B687" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C687" s="6">
-        <v>10.19</v>
+        <v>3.36</v>
       </c>
       <c r="D687" t="s">
         <v>303</v>
@@ -10582,10 +10582,10 @@
         <v>294</v>
       </c>
       <c r="B688" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C688" s="6">
-        <v>14.4</v>
+        <v>10.19</v>
       </c>
       <c r="D688" t="s">
         <v>303</v>
@@ -10596,10 +10596,10 @@
         <v>294</v>
       </c>
       <c r="B689" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C689" s="6">
-        <v>14.39</v>
+        <v>14.4</v>
       </c>
       <c r="D689" t="s">
         <v>303</v>
@@ -10610,10 +10610,10 @@
         <v>294</v>
       </c>
       <c r="B690" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C690" s="6">
-        <v>11.52</v>
+        <v>14.39</v>
       </c>
       <c r="D690" t="s">
         <v>303</v>
@@ -10624,10 +10624,10 @@
         <v>294</v>
       </c>
       <c r="B691" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C691" s="6">
-        <v>12</v>
+        <v>11.52</v>
       </c>
       <c r="D691" t="s">
         <v>303</v>
@@ -10638,7 +10638,7 @@
         <v>294</v>
       </c>
       <c r="B692" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C692" s="6">
         <v>12</v>
@@ -10652,12 +10652,26 @@
         <v>294</v>
       </c>
       <c r="B693" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C693" s="6">
         <v>12</v>
       </c>
       <c r="D693" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="694" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A694" t="s">
+        <v>294</v>
+      </c>
+      <c r="B694" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C694" s="6">
+        <v>12</v>
+      </c>
+      <c r="D694" t="s">
         <v>303</v>
       </c>
     </row>

--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Garretts Reports\Sales Report App\Excell Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3789B771-1965-4680-B679-5831B77082B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB36A14E-B9CC-4040-ABCA-9F4791F97C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1905" windowWidth="12120" windowHeight="19695" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="12120" windowHeight="19695" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -10350,7 +10350,7 @@
         <v>22</v>
       </c>
       <c r="C662" s="6">
-        <v>10</v>
+        <v>2.75</v>
       </c>
       <c r="D662" t="s">
         <v>140</v>
@@ -10363,6 +10363,9 @@
       <c r="B663" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="C663" s="6">
+        <v>3.25</v>
+      </c>
       <c r="D663" t="s">
         <v>140</v>
       </c>
@@ -10431,7 +10434,7 @@
         <v>22</v>
       </c>
       <c r="C672" s="6">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="D672" t="s">
         <v>140</v>
@@ -10445,7 +10448,7 @@
         <v>23</v>
       </c>
       <c r="C673" s="6">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="D673" t="s">
         <v>140</v>

--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Garretts Reports\Sales Report App\Excell Sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svr01\home\gfetzer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB36A14E-B9CC-4040-ABCA-9F4791F97C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{09C0E4CF-AD64-4515-9816-54A43B890398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="12120" windowHeight="19695" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
+    <workbookView xWindow="10365" yWindow="2820" windowWidth="24600" windowHeight="15750" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1901" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="340">
   <si>
     <t>BGC10</t>
   </si>
@@ -1042,6 +1042,9 @@
   </si>
   <si>
     <t>RS10</t>
+  </si>
+  <si>
+    <t>TikTok</t>
   </si>
 </sst>
 </file>
@@ -1439,7 +1442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6055176-08B8-4018-B9DF-7F26AB5DB49D}">
-  <dimension ref="A1:K694"/>
+  <dimension ref="A1:K698"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -10678,6 +10681,34 @@
         <v>303</v>
       </c>
     </row>
+    <row r="697" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A697" t="s">
+        <v>339</v>
+      </c>
+      <c r="B697" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C697" s="6">
+        <v>17.489999999999998</v>
+      </c>
+      <c r="D697" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="698" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A698" t="s">
+        <v>339</v>
+      </c>
+      <c r="B698" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C698" s="6">
+        <v>28.99</v>
+      </c>
+      <c r="D698" t="s">
+        <v>146</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svr01\home\gfetzer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{09C0E4CF-AD64-4515-9816-54A43B890398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6175D4-E88C-4EF7-8DCB-C7E428C43A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10365" yWindow="2820" windowWidth="24600" windowHeight="15750" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
+    <workbookView xWindow="45510" yWindow="3030" windowWidth="24600" windowHeight="15750" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1913" uniqueCount="340">
   <si>
     <t>BGC10</t>
   </si>
@@ -1442,7 +1442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6055176-08B8-4018-B9DF-7F26AB5DB49D}">
-  <dimension ref="A1:K698"/>
+  <dimension ref="A1:K700"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -10709,6 +10709,34 @@
         <v>146</v>
       </c>
     </row>
+    <row r="699" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A699" t="s">
+        <v>339</v>
+      </c>
+      <c r="B699" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C699" s="6">
+        <v>199.99</v>
+      </c>
+      <c r="D699" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="700" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A700" t="s">
+        <v>339</v>
+      </c>
+      <c r="B700" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C700" s="6">
+        <v>359.99</v>
+      </c>
+      <c r="D700" t="s">
+        <v>142</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
